--- a/SPC26S1 - 05 May v2.xlsx
+++ b/SPC26S1 - 05 May v2.xlsx
@@ -2543,7 +2543,7 @@
     <t>Cells you edit</t>
   </si>
   <si>
-    <t>Four columns are shaded pale yellow and are the ones meant to be edited here: Claim Status (A), Notes (B), Processed Date (C) and Latest Date Worked (K). Claim Status has a drop-down of the statuses already in use - it is a suggestion, not a restriction, so you can type anything.</t>
+    <t>Four columns are shaded pale yellow and are the ones meant to be edited here: Claim Status (A), Notes (B), Processed Date (C) and Latest Date Worked (K). Claim Status has a drop-down list, and anything not on the list is rejected so a typo cannot slip in. To add a new status, edit the list under Data &gt; Data Validation.</t>
   </si>
   <si>
     <t>Example of the expected format - Claim Status: "Denied";  Notes: "Corrected service line 1 - resubmitted";  Processed Date: "06/25/2026";  Latest Date Worked: "08/12/2026".</t>
@@ -2624,7 +2624,7 @@
     <t xml:space="preserve">Expecting ins reply - DND as medical necessity - Jess sent MR </t>
   </si>
   <si>
-    <t>Statuses currently in use: Denied, Finalized, Not found, PAID, Pending, Received, Rejected, Under Review.</t>
+    <t>Statuses on the drop-down: Denied, Finalized, Not found, PAID, Pending, Received, Rejected, Under Review.</t>
   </si>
   <si>
     <t>540 days</t>
@@ -2636,7 +2636,7 @@
     <t>Every specialty sheet is sorted in four groups: Rejected claims at the very top, then claims with an empty Latest Date Worked (column K), then the other open claims, and Finalized and PAID claims at the bottom (a Finalized or PAID claim with an empty Latest Date Worked stays in the empty Latest Date Worked group). Within each group, rows are ordered by how close the claim is to its primary payer's timely filing deadline. Days Until Deadline (column L) carries the count: five days or less left is shaded red, a negative number means the filing window has already closed, and a blank means no limit is on file for that payer.</t>
   </si>
   <si>
-    <t>Deadline order within each group, with the colour band each row gets, counted on 19 September 2026:</t>
+    <t>Deadline order within each group, with the colour band each row gets (these counts update automatically):</t>
   </si>
   <si>
     <t xml:space="preserve">    1 - Due in 5 days or less: 3</t>
@@ -2654,7 +2654,7 @@
     <t xml:space="preserve">    5 - No limit on file: 11</t>
   </si>
   <si>
-    <t>'SPC26S1 - 00 Master v2.xlsx' (same folder) holds all 477 claims for 2026 S1. Its Claim Status and Notes columns are formulas that read this file, so anything you type in columns A and B here shows up there. Keep both files in the same folder, keep the file name unchanged, and save this file before opening the master.</t>
+    <t>'SPC26S1 - 00 Master v2.xlsx' (same folder) holds every claim for 2026 S1. Its Claim Status and Notes columns are formulas that read this file, so anything you type in columns A and B here shows up there. Keep both files in the same folder, keep the file name unchanged, and save this file before opening the master.</t>
   </si>
   <si>
     <t>Resubmitted again - Aisha review Adlers status on the AHCCCS portal. He is showing active ins 2012 - Rendering OON with Medicaid AHCCCS - Confirming with Bri - DOS we were working on 05/01/2026</t>
@@ -7569,7 +7569,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="Claim Status" prompt="Pick a status, or type a new one." sqref="A2:A31" xr:uid="{00000000-0002-0000-0000-000000000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorStyle="stop" errorTitle="Claim Status" error="Choose a status from the drop-down list. To add a new status, edit the list under Data &gt; Data Validation." promptTitle="Claim Status" prompt="Pick a status from the list." sqref="A2:A1000">
       <formula1>"Denied,Finalized,Not found,PAID,Pending,Received,Rejected,Under Review"</formula1>
     </dataValidation>
   </dataValidations>
@@ -7580,7 +7580,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:AN48"/>
+  <dimension ref="A1:AN35"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
@@ -11600,14 +11600,6 @@
       <c r="AN35" s="5" t="s">
         <v>179</v>
       </c>
-    </row>
-    <row r="47" spans="1:40" x14ac:dyDescent="0.25">
-      <c r="F47" s="13"/>
-    </row>
-    <row r="48" spans="1:40" x14ac:dyDescent="0.25">
-      <c r="G48" s="13"/>
-      <c r="H48" s="13"/>
-      <c r="J48" s="14"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AN35" xr:uid="{00000000-0009-0000-0000-000001000000}"/>
@@ -11706,7 +11698,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="Claim Status" prompt="Pick a status, or type a new one." sqref="A2:A35" xr:uid="{00000000-0002-0000-0100-000000000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorStyle="stop" errorTitle="Claim Status" error="Choose a status from the drop-down list. To add a new status, edit the list under Data &gt; Data Validation." promptTitle="Claim Status" prompt="Pick a status from the list." sqref="A2:A1000">
       <formula1>"Denied,Finalized,Not found,PAID,Pending,Received,Rejected,Under Review"</formula1>
     </dataValidation>
   </dataValidations>
@@ -12674,7 +12666,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="Claim Status" prompt="Pick a status, or type a new one." sqref="A2:A7" xr:uid="{00000000-0002-0000-0200-000000000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorStyle="stop" errorTitle="Claim Status" error="Choose a status from the drop-down list. To add a new status, edit the list under Data &gt; Data Validation." promptTitle="Claim Status" prompt="Pick a status from the list." sqref="A2:A1000">
       <formula1>"Denied,Finalized,Not found,PAID,Pending,Received,Rejected,Under Review"</formula1>
     </dataValidation>
   </dataValidations>
@@ -15422,7 +15414,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="Claim Status" prompt="Pick a status, or type a new one." sqref="A2:A23" xr:uid="{00000000-0002-0000-0300-000000000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorStyle="stop" errorTitle="Claim Status" error="Choose a status from the drop-down list. To add a new status, edit the list under Data &gt; Data Validation." promptTitle="Claim Status" prompt="Pick a status from the list." sqref="A2:A1000">
       <formula1>"Denied,Finalized,Not found,PAID,Pending,Received,Rejected,Under Review"</formula1>
     </dataValidation>
   </dataValidations>
@@ -17389,7 +17381,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="Claim Status" prompt="Pick a status, or type a new one." sqref="A2:A16" xr:uid="{00000000-0002-0000-0400-000000000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorStyle="stop" errorTitle="Claim Status" error="Choose a status from the drop-down list. To add a new status, edit the list under Data &gt; Data Validation." promptTitle="Claim Status" prompt="Pick a status from the list." sqref="A2:A1000">
       <formula1>"Denied,Finalized,Not found,PAID,Pending,Received,Rejected,Under Review"</formula1>
     </dataValidation>
   </dataValidations>
@@ -17418,8 +17410,9 @@
       <c r="A2" s="9"/>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A3" s="9" t="s">
-        <v>540</v>
+      <c r="A3" s="9" t="str">
+        <f>COUNTA(BH!$D$2:$D$1000,DME!$D$2:$D$1000,GAE!$D$2:$D$1000,ORTHO!$D$2:$D$1000,US!$D$2:$D$1000)&amp;" claims with a date of service in 2026-05 May, split into one sheet per specialty: BH, DME, GAE, ORTHO, US."</f>
+        <v>107 claims with a date of service in 2026-05 May, split into one sheet per specialty: BH, DME, GAE, ORTHO, US.</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
@@ -17441,28 +17434,33 @@
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A8" s="9" t="s">
-        <v>543</v>
+      <c r="A8" s="9" t="str">
+        <f>"    1 - Due in 5 days or less: "&amp;SUM(COUNTIFS(BH!$L$2:$L$1000,"&gt;=0",BH!$L$2:$L$1000,"&lt;=5"),COUNTIFS(DME!$L$2:$L$1000,"&gt;=0",DME!$L$2:$L$1000,"&lt;=5"),COUNTIFS(GAE!$L$2:$L$1000,"&gt;=0",GAE!$L$2:$L$1000,"&lt;=5"),COUNTIFS(ORTHO!$L$2:$L$1000,"&gt;=0",ORTHO!$L$2:$L$1000,"&lt;=5"),COUNTIFS(US!$L$2:$L$1000,"&gt;=0",US!$L$2:$L$1000,"&lt;=5"))</f>
+        <v>    1 - Due in 5 days or less: 0</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A9" s="9" t="s">
-        <v>544</v>
+      <c r="A9" s="9" t="str">
+        <f>"    2 - Due in 6-30 days: "&amp;SUM(COUNTIFS(BH!$L$2:$L$1000,"&gt;5",BH!$L$2:$L$1000,"&lt;=30"),COUNTIFS(DME!$L$2:$L$1000,"&gt;5",DME!$L$2:$L$1000,"&lt;=30"),COUNTIFS(GAE!$L$2:$L$1000,"&gt;5",GAE!$L$2:$L$1000,"&lt;=30"),COUNTIFS(ORTHO!$L$2:$L$1000,"&gt;5",ORTHO!$L$2:$L$1000,"&lt;=30"),COUNTIFS(US!$L$2:$L$1000,"&gt;5",US!$L$2:$L$1000,"&lt;=30"))</f>
+        <v>    2 - Due in 6-30 days: 1</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A10" s="9" t="s">
-        <v>545</v>
+      <c r="A10" s="9" t="str">
+        <f>"    3 - Due in 31+ days: "&amp;SUM(COUNTIFS(BH!$L$2:$L$1000,"&gt;30"),COUNTIFS(DME!$L$2:$L$1000,"&gt;30"),COUNTIFS(GAE!$L$2:$L$1000,"&gt;30"),COUNTIFS(ORTHO!$L$2:$L$1000,"&gt;30"),COUNTIFS(US!$L$2:$L$1000,"&gt;30"))</f>
+        <v>    3 - Due in 31+ days: 37</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A11" s="9" t="s">
-        <v>546</v>
+      <c r="A11" s="9" t="str">
+        <f>"    4 - Past deadline: "&amp;SUM(COUNTIFS(BH!$L$2:$L$1000,"&lt;0"),COUNTIFS(DME!$L$2:$L$1000,"&lt;0"),COUNTIFS(GAE!$L$2:$L$1000,"&lt;0"),COUNTIFS(ORTHO!$L$2:$L$1000,"&lt;0"),COUNTIFS(US!$L$2:$L$1000,"&lt;0"))</f>
+        <v>    4 - Past deadline: 58</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A12" s="9" t="s">
-        <v>547</v>
+      <c r="A12" s="9" t="str">
+        <f>"    5 - No limit on file: "&amp;SUM(COUNTIFS(BH!$D$2:$D$1000,"&lt;&gt;",BH!$L$2:$L$1000,""),COUNTIFS(DME!$D$2:$D$1000,"&lt;&gt;",DME!$L$2:$L$1000,""),COUNTIFS(GAE!$D$2:$D$1000,"&lt;&gt;",GAE!$L$2:$L$1000,""),COUNTIFS(ORTHO!$D$2:$D$1000,"&lt;&gt;",ORTHO!$L$2:$L$1000,""),COUNTIFS(US!$D$2:$D$1000,"&lt;&gt;",US!$L$2:$L$1000,""))</f>
+        <v>    5 - No limit on file: 11</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.25">

--- a/SPC26S1 - 05 May v2.xlsx
+++ b/SPC26S1 - 05 May v2.xlsx
@@ -2811,7 +2811,7 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="103">
+  <dxfs count="104">
     <dxf>
       <font>
         <color rgb="FF1F4E79"/>
@@ -3810,9 +3810,13 @@
       </fill>
     </dxf>
     <dxf>
+      <font>
+        <b/>
+        <color rgb="FF000000"/>
+      </font>
       <fill>
         <patternFill patternType="solid">
-          <bgColor rgb="FFF8CBAD"/>
+          <bgColor rgb="FFFF9933"/>
         </patternFill>
       </fill>
     </dxf>
@@ -3834,6 +3838,13 @@
       <fill>
         <patternFill patternType="solid">
           <bgColor rgb="FFBFBFBF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFCE4E4"/>
         </patternFill>
       </fill>
     </dxf>
@@ -7559,7 +7570,10 @@
       <formula>TRIM($A2)="Under Review"</formula>
     </cfRule>
     <cfRule type="expression" dxfId="100" priority="21">
-      <formula>TRIM($A2)="Denied"</formula>
+      <formula>AND(TRIM($A2)="Denied",$K2="")</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="103" priority="24">
+      <formula>AND(TRIM($A2)="Denied",$K2&lt;&gt;"")</formula>
     </cfRule>
     <cfRule type="expression" dxfId="101" priority="22">
       <formula>TRIM($A2)="Rejected"</formula>
@@ -11688,7 +11702,10 @@
       <formula>TRIM($A2)="Under Review"</formula>
     </cfRule>
     <cfRule type="expression" dxfId="100" priority="26">
-      <formula>TRIM($A2)="Denied"</formula>
+      <formula>AND(TRIM($A2)="Denied",$K2="")</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="103" priority="29">
+      <formula>AND(TRIM($A2)="Denied",$K2&lt;&gt;"")</formula>
     </cfRule>
     <cfRule type="expression" dxfId="101" priority="27">
       <formula>TRIM($A2)="Rejected"</formula>
@@ -12656,7 +12673,10 @@
       <formula>TRIM($A2)="Under Review"</formula>
     </cfRule>
     <cfRule type="expression" dxfId="100" priority="26">
-      <formula>TRIM($A2)="Denied"</formula>
+      <formula>AND(TRIM($A2)="Denied",$K2="")</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="103" priority="29">
+      <formula>AND(TRIM($A2)="Denied",$K2&lt;&gt;"")</formula>
     </cfRule>
     <cfRule type="expression" dxfId="101" priority="27">
       <formula>TRIM($A2)="Rejected"</formula>
@@ -15404,7 +15424,10 @@
       <formula>TRIM($A2)="Under Review"</formula>
     </cfRule>
     <cfRule type="expression" dxfId="100" priority="26">
-      <formula>TRIM($A2)="Denied"</formula>
+      <formula>AND(TRIM($A2)="Denied",$K2="")</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="103" priority="29">
+      <formula>AND(TRIM($A2)="Denied",$K2&lt;&gt;"")</formula>
     </cfRule>
     <cfRule type="expression" dxfId="101" priority="27">
       <formula>TRIM($A2)="Rejected"</formula>
@@ -17371,7 +17394,10 @@
       <formula>TRIM($A2)="Under Review"</formula>
     </cfRule>
     <cfRule type="expression" dxfId="100" priority="26">
-      <formula>TRIM($A2)="Denied"</formula>
+      <formula>AND(TRIM($A2)="Denied",$K2="")</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="103" priority="29">
+      <formula>AND(TRIM($A2)="Denied",$K2&lt;&gt;"")</formula>
     </cfRule>
     <cfRule type="expression" dxfId="101" priority="27">
       <formula>TRIM($A2)="Rejected"</formula>
@@ -17395,7 +17421,7 @@
   <sheetPr>
     <tabColor rgb="FF1F4E79"/>
   </sheetPr>
-  <dimension ref="A1:A49"/>
+  <dimension ref="A1:A50"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="118" customWidth="1"/>
@@ -17624,14 +17650,14 @@
     <row r="45" spans="1:1">
       <c r="A45" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Under Review - orange</t>
+          <t xml:space="preserve">    Under Review - bright orange, bold (follow up on these)</t>
         </is>
       </c>
     </row>
     <row r="46" spans="1:1">
       <c r="A46" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Denied - red</t>
+          <t xml:space="preserve">    Denied, not worked yet (Latest Date Worked empty) - red</t>
         </is>
       </c>
     </row>
@@ -17651,6 +17677,13 @@
     </row>
     <row r="49" spans="1:1">
       <c r="A49" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Denied, already worked (Latest Date Worked filled in) - light pink</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" spans="1:1">
+      <c r="A50" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">Any other status is left unshaded.</t>
         </is>
@@ -17697,6 +17730,11 @@
       <formula>TRUE</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="A49">
+    <cfRule type="expression" dxfId="103" priority="9">
+      <formula>TRUE</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/SPC26S1 - 05 May v2.xlsx
+++ b/SPC26S1 - 05 May v2.xlsx
@@ -2636,7 +2636,7 @@
     <t>Every specialty sheet is sorted in four groups: Rejected claims at the very top, then claims with an empty Latest Date Worked (column K), then the other open claims, and Finalized and PAID claims at the bottom (a Finalized or PAID claim with an empty Latest Date Worked stays in the empty Latest Date Worked group). Within each group, rows are ordered by how close the claim is to its primary payer's timely filing deadline. Days Until Deadline (column L) carries the count: five days or less left is shaded red, a negative number means the filing window has already closed, and a blank means no limit is on file for that payer.</t>
   </si>
   <si>
-    <t>Deadline order within each group, with the colour band each row gets (these counts update automatically):</t>
+    <t>Deadline order within each group, with the colour band each row gets (these counts update automatically; Finalized claims with a Latest Date Worked have their deadline cells left empty and are not counted):</t>
   </si>
   <si>
     <t xml:space="preserve">    1 - Due in 5 days or less: 3</t>
@@ -4349,14 +4349,15 @@
         <v>-70</v>
       </c>
       <c r="M2" s="12" t="str">
-        <f ca="1">IF($C2="","",$C2+180-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A2)="Finalized",$K2&lt;&gt;""),"",IF($C2="","",$C2+180-TODAY()))</f>
         <v/>
       </c>
       <c r="N2" s="12" t="str">
-        <f ca="1">IF($C2="","",$C2+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A2)="Finalized",$K2&lt;&gt;""),"",IF($C2="","",$C2+365-TODAY()))</f>
         <v/>
       </c>
       <c r="O2" s="6">
+        <f>IF(AND(TRIM($A2)="Finalized",$K2&lt;&gt;""),"",DATE(2026,7,30))</f>
         <v>46233</v>
       </c>
       <c r="P2" s="5" t="s">
@@ -4456,14 +4457,15 @@
         <v>-14</v>
       </c>
       <c r="M3" s="12">
-        <f ca="1">IF($C3="","",$C3+180-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A3)="Finalized",$K3&lt;&gt;""),"",IF($C3="","",$C3+180-TODAY()))</f>
         <v>72</v>
       </c>
       <c r="N3" s="12">
-        <f ca="1">IF($C3="","",$C3+180-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A3)="Finalized",$K3&lt;&gt;""),"",IF($C3="","",$C3+180-TODAY()))</f>
         <v>72</v>
       </c>
       <c r="O3" s="6">
+        <f>IF(AND(TRIM($A3)="Finalized",$K3&lt;&gt;""),"",DATE(2026,9,24))</f>
         <v>46289</v>
       </c>
       <c r="P3" s="5" t="s">
@@ -4739,14 +4741,15 @@
         <v>-57</v>
       </c>
       <c r="M6" s="12" t="str">
-        <f ca="1">IF($C6="","",$C6+180-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A6)="Finalized",$K6&lt;&gt;""),"",IF($C6="","",$C6+180-TODAY()))</f>
         <v/>
       </c>
       <c r="N6" s="12" t="str">
-        <f ca="1">IF($C6="","",$C6+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A6)="Finalized",$K6&lt;&gt;""),"",IF($C6="","",$C6+365-TODAY()))</f>
         <v/>
       </c>
       <c r="O6" s="6">
+        <f>IF(AND(TRIM($A6)="Finalized",$K6&lt;&gt;""),"",DATE(2026,8,12))</f>
         <v>46246</v>
       </c>
       <c r="P6" s="5" t="s">
@@ -4846,14 +4849,15 @@
         <v>-57</v>
       </c>
       <c r="M7" s="12" t="str">
-        <f ca="1">IF($C7="","",$C7+180-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A7)="Finalized",$K7&lt;&gt;""),"",IF($C7="","",$C7+180-TODAY()))</f>
         <v/>
       </c>
       <c r="N7" s="12" t="str">
-        <f ca="1">IF($C7="","",$C7+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A7)="Finalized",$K7&lt;&gt;""),"",IF($C7="","",$C7+365-TODAY()))</f>
         <v/>
       </c>
       <c r="O7" s="6">
+        <f>IF(AND(TRIM($A7)="Finalized",$K7&lt;&gt;""),"",DATE(2026,8,12))</f>
         <v>46246</v>
       </c>
       <c r="P7" s="5" t="s">
@@ -4953,14 +4957,15 @@
         <v>-55</v>
       </c>
       <c r="M8" s="12" t="str">
-        <f ca="1">IF($C8="","",$C8+90-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A8)="Finalized",$K8&lt;&gt;""),"",IF($C8="","",$C8+90-TODAY()))</f>
         <v/>
       </c>
       <c r="N8" s="12" t="str">
-        <f ca="1">IF($C8="","",$C8+90-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A8)="Finalized",$K8&lt;&gt;""),"",IF($C8="","",$C8+90-TODAY()))</f>
         <v/>
       </c>
       <c r="O8" s="6">
+        <f>IF(AND(TRIM($A8)="Finalized",$K8&lt;&gt;""),"",DATE(2026,8,14))</f>
         <v>46248</v>
       </c>
       <c r="P8" s="5" t="s">
@@ -5062,14 +5067,15 @@
         <v>-51</v>
       </c>
       <c r="M9" s="12">
-        <f ca="1">IF($C9="","",$C9+180-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A9)="Finalized",$K9&lt;&gt;""),"",IF($C9="","",$C9+180-TODAY()))</f>
         <v>66</v>
       </c>
       <c r="N9" s="12">
-        <f ca="1">IF($C9="","",$C9+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A9)="Finalized",$K9&lt;&gt;""),"",IF($C9="","",$C9+365-TODAY()))</f>
         <v>251</v>
       </c>
       <c r="O9" s="6">
+        <f>IF(AND(TRIM($A9)="Finalized",$K9&lt;&gt;""),"",DATE(2026,8,18))</f>
         <v>46252</v>
       </c>
       <c r="P9" s="5" t="s">
@@ -5175,14 +5181,15 @@
         <v>-51</v>
       </c>
       <c r="M10" s="12">
-        <f ca="1">IF($C10="","",$C10+180-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A10)="Finalized",$K10&lt;&gt;""),"",IF($C10="","",$C10+180-TODAY()))</f>
         <v>60</v>
       </c>
       <c r="N10" s="12">
-        <f ca="1">IF($C10="","",$C10+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A10)="Finalized",$K10&lt;&gt;""),"",IF($C10="","",$C10+365-TODAY()))</f>
         <v>245</v>
       </c>
       <c r="O10" s="6">
+        <f>IF(AND(TRIM($A10)="Finalized",$K10&lt;&gt;""),"",DATE(2026,8,18))</f>
         <v>46252</v>
       </c>
       <c r="P10" s="5" t="s">
@@ -5286,14 +5293,15 @@
         <v>-49</v>
       </c>
       <c r="M11" s="12" t="str">
-        <f ca="1">IF($C11="","",$C11+180-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A11)="Finalized",$K11&lt;&gt;""),"",IF($C11="","",$C11+180-TODAY()))</f>
         <v/>
       </c>
       <c r="N11" s="12" t="str">
-        <f ca="1">IF($C11="","",$C11+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A11)="Finalized",$K11&lt;&gt;""),"",IF($C11="","",$C11+365-TODAY()))</f>
         <v/>
       </c>
       <c r="O11" s="6">
+        <f>IF(AND(TRIM($A11)="Finalized",$K11&lt;&gt;""),"",DATE(2026,8,20))</f>
         <v>46254</v>
       </c>
       <c r="P11" s="5" t="s">
@@ -5395,14 +5403,15 @@
         <v>-49</v>
       </c>
       <c r="M12" s="12">
-        <f ca="1">IF($C12="","",$C12+180-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A12)="Finalized",$K12&lt;&gt;""),"",IF($C12="","",$C12+180-TODAY()))</f>
         <v>60</v>
       </c>
       <c r="N12" s="12">
-        <f ca="1">IF($C12="","",$C12+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A12)="Finalized",$K12&lt;&gt;""),"",IF($C12="","",$C12+365-TODAY()))</f>
         <v>245</v>
       </c>
       <c r="O12" s="6">
+        <f>IF(AND(TRIM($A12)="Finalized",$K12&lt;&gt;""),"",DATE(2026,8,20))</f>
         <v>46254</v>
       </c>
       <c r="P12" s="5" t="s">
@@ -5508,14 +5517,15 @@
         <v>-42</v>
       </c>
       <c r="M13" s="12">
-        <f ca="1">IF($C13="","",$C13+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A13)="Finalized",$K13&lt;&gt;""),"",IF($C13="","",$C13+365-TODAY()))</f>
         <v>253</v>
       </c>
       <c r="N13" s="12">
-        <f ca="1">IF($C13="","",$C13+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A13)="Finalized",$K13&lt;&gt;""),"",IF($C13="","",$C13+365-TODAY()))</f>
         <v>253</v>
       </c>
       <c r="O13" s="6">
+        <f>IF(AND(TRIM($A13)="Finalized",$K13&lt;&gt;""),"",DATE(2026,8,27))</f>
         <v>46261</v>
       </c>
       <c r="P13" s="5" t="s">
@@ -5619,14 +5629,15 @@
         <v>208</v>
       </c>
       <c r="M14" s="12">
-        <f ca="1">IF($C14="","",$C14+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A14)="Finalized",$K14&lt;&gt;""),"",IF($C14="","",$C14+365-TODAY()))</f>
         <v>252</v>
       </c>
       <c r="N14" s="12">
-        <f ca="1">IF($C14="","",$C14+120-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A14)="Finalized",$K14&lt;&gt;""),"",IF($C14="","",$C14+120-TODAY()))</f>
         <v>7</v>
       </c>
       <c r="O14" s="6">
+        <f>IF(AND(TRIM($A14)="Finalized",$K14&lt;&gt;""),"",DATE(2027,5,4))</f>
         <v>46511</v>
       </c>
       <c r="P14" s="5" t="s">
@@ -5730,14 +5741,15 @@
         <v>209</v>
       </c>
       <c r="M15" s="12">
-        <f ca="1">IF($C15="","",$C15+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A15)="Finalized",$K15&lt;&gt;""),"",IF($C15="","",$C15+365-TODAY()))</f>
         <v>258</v>
       </c>
       <c r="N15" s="12">
-        <f ca="1">IF($C15="","",$C15+120-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A15)="Finalized",$K15&lt;&gt;""),"",IF($C15="","",$C15+120-TODAY()))</f>
         <v>13</v>
       </c>
       <c r="O15" s="6">
+        <f>IF(AND(TRIM($A15)="Finalized",$K15&lt;&gt;""),"",DATE(2027,5,5))</f>
         <v>46512</v>
       </c>
       <c r="P15" s="5" t="s">
@@ -5843,14 +5855,15 @@
         <v>217</v>
       </c>
       <c r="M16" s="12">
-        <f ca="1">IF($C16="","",$C16+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A16)="Finalized",$K16&lt;&gt;""),"",IF($C16="","",$C16+365-TODAY()))</f>
         <v>258</v>
       </c>
       <c r="N16" s="12">
-        <f ca="1">IF($C16="","",$C16+120-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A16)="Finalized",$K16&lt;&gt;""),"",IF($C16="","",$C16+120-TODAY()))</f>
         <v>13</v>
       </c>
       <c r="O16" s="6">
+        <f>IF(AND(TRIM($A16)="Finalized",$K16&lt;&gt;""),"",DATE(2027,5,13))</f>
         <v>46520</v>
       </c>
       <c r="P16" s="5" t="s">
@@ -5956,14 +5969,15 @@
         <v>219</v>
       </c>
       <c r="M17" s="12">
-        <f ca="1">IF($C17="","",$C17+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A17)="Finalized",$K17&lt;&gt;""),"",IF($C17="","",$C17+365-TODAY()))</f>
         <v>258</v>
       </c>
       <c r="N17" s="12">
-        <f ca="1">IF($C17="","",$C17+120-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A17)="Finalized",$K17&lt;&gt;""),"",IF($C17="","",$C17+120-TODAY()))</f>
         <v>13</v>
       </c>
       <c r="O17" s="6">
+        <f>IF(AND(TRIM($A17)="Finalized",$K17&lt;&gt;""),"",DATE(2027,5,15))</f>
         <v>46522</v>
       </c>
       <c r="P17" s="5" t="s">
@@ -6069,14 +6083,15 @@
         <v>232</v>
       </c>
       <c r="M18" s="12">
-        <f ca="1">IF($C18="","",$C18+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A18)="Finalized",$K18&lt;&gt;""),"",IF($C18="","",$C18+365-TODAY()))</f>
         <v>258</v>
       </c>
       <c r="N18" s="12">
-        <f ca="1">IF($C18="","",$C18+120-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A18)="Finalized",$K18&lt;&gt;""),"",IF($C18="","",$C18+120-TODAY()))</f>
         <v>13</v>
       </c>
       <c r="O18" s="6">
+        <f>IF(AND(TRIM($A18)="Finalized",$K18&lt;&gt;""),"",DATE(2027,5,28))</f>
         <v>46535</v>
       </c>
       <c r="P18" s="5" t="s">
@@ -6180,14 +6195,15 @@
         <v>-64</v>
       </c>
       <c r="M19" s="12" t="str">
-        <f ca="1">IF($C19="","",$C19+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A19)="Finalized",$K19&lt;&gt;""),"",IF($C19="","",$C19+365-TODAY()))</f>
         <v/>
       </c>
       <c r="N19" s="12" t="str">
-        <f ca="1">IF($C19="","",$C19+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A19)="Finalized",$K19&lt;&gt;""),"",IF($C19="","",$C19+365-TODAY()))</f>
         <v/>
       </c>
       <c r="O19" s="6">
+        <f>IF(AND(TRIM($A19)="Finalized",$K19&lt;&gt;""),"",DATE(2026,8,5))</f>
         <v>46239</v>
       </c>
       <c r="P19" s="5" t="s">
@@ -6289,14 +6305,15 @@
         <v>-82</v>
       </c>
       <c r="M20" s="12">
-        <f ca="1">IF($C20="","",$C20+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A20)="Finalized",$K20&lt;&gt;""),"",IF($C20="","",$C20+365-TODAY()))</f>
         <v>279</v>
       </c>
       <c r="N20" s="12">
-        <f ca="1">IF($C20="","",$C20+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A20)="Finalized",$K20&lt;&gt;""),"",IF($C20="","",$C20+365-TODAY()))</f>
         <v>279</v>
       </c>
       <c r="O20" s="6">
+        <f>IF(AND(TRIM($A20)="Finalized",$K20&lt;&gt;""),"",DATE(2026,7,18))</f>
         <v>46221</v>
       </c>
       <c r="P20" s="5" t="s">
@@ -6769,20 +6786,21 @@
       <c r="K25" s="3">
         <v>46276</v>
       </c>
-      <c r="L25" s="12">
+      <c t="str" r="L25" s="12">
         <f ca="1">IF($O25="","",$O25-TODAY())</f>
-        <v>-14</v>
-      </c>
-      <c r="M25" s="12">
-        <f ca="1">IF($C25="","",$C25+180-TODAY())</f>
-        <v>129</v>
-      </c>
-      <c r="N25" s="12">
-        <f ca="1">IF($C25="","",$C25+180-TODAY())</f>
-        <v>129</v>
-      </c>
-      <c r="O25" s="6">
-        <v>46289</v>
+        <v/>
+      </c>
+      <c t="str" r="M25" s="12">
+        <f ca="1">IF(AND(TRIM($A25)="Finalized",$K25&lt;&gt;""),"",IF($C25="","",$C25+180-TODAY()))</f>
+        <v/>
+      </c>
+      <c t="str" r="N25" s="12">
+        <f ca="1">IF(AND(TRIM($A25)="Finalized",$K25&lt;&gt;""),"",IF($C25="","",$C25+180-TODAY()))</f>
+        <v/>
+      </c>
+      <c t="str" r="O25" s="6">
+        <f>IF(AND(TRIM($A25)="Finalized",$K25&lt;&gt;""),"",DATE(2026,9,24))</f>
+        <v/>
       </c>
       <c r="P25" s="5" t="s">
         <v>103</v>
@@ -6886,20 +6904,21 @@
       <c r="K26" s="3">
         <v>46276</v>
       </c>
-      <c r="L26" s="12">
+      <c t="str" r="L26" s="12">
         <f ca="1">IF($O26="","",$O26-TODAY())</f>
-        <v>205</v>
-      </c>
-      <c r="M26" s="12">
-        <f ca="1">IF($C26="","",$C26+365-TODAY())</f>
-        <v>328</v>
-      </c>
-      <c r="N26" s="12">
-        <f ca="1">IF($C26="","",$C26+120-TODAY())</f>
-        <v>83</v>
-      </c>
-      <c r="O26" s="6">
-        <v>46508</v>
+        <v/>
+      </c>
+      <c t="str" r="M26" s="12">
+        <f ca="1">IF(AND(TRIM($A26)="Finalized",$K26&lt;&gt;""),"",IF($C26="","",$C26+365-TODAY()))</f>
+        <v/>
+      </c>
+      <c t="str" r="N26" s="12">
+        <f ca="1">IF(AND(TRIM($A26)="Finalized",$K26&lt;&gt;""),"",IF($C26="","",$C26+120-TODAY()))</f>
+        <v/>
+      </c>
+      <c t="str" r="O26" s="6">
+        <f>IF(AND(TRIM($A26)="Finalized",$K26&lt;&gt;""),"",DATE(2027,5,1))</f>
+        <v/>
       </c>
       <c r="P26" s="5" t="s">
         <v>50</v>
@@ -6995,20 +7014,21 @@
       <c r="K27" s="3">
         <v>46252</v>
       </c>
-      <c r="L27" s="12">
+      <c t="str" r="L27" s="12">
         <f ca="1">IF($O27="","",$O27-TODAY())</f>
-        <v>211</v>
-      </c>
-      <c r="M27" s="12">
-        <f ca="1">IF($C27="","",$C27+365-TODAY())</f>
-        <v>258</v>
-      </c>
-      <c r="N27" s="12">
-        <f ca="1">IF($C27="","",$C27+120-TODAY())</f>
-        <v>13</v>
-      </c>
-      <c r="O27" s="6">
-        <v>46514</v>
+        <v/>
+      </c>
+      <c t="str" r="M27" s="12">
+        <f ca="1">IF(AND(TRIM($A27)="Finalized",$K27&lt;&gt;""),"",IF($C27="","",$C27+365-TODAY()))</f>
+        <v/>
+      </c>
+      <c t="str" r="N27" s="12">
+        <f ca="1">IF(AND(TRIM($A27)="Finalized",$K27&lt;&gt;""),"",IF($C27="","",$C27+120-TODAY()))</f>
+        <v/>
+      </c>
+      <c t="str" r="O27" s="6">
+        <f>IF(AND(TRIM($A27)="Finalized",$K27&lt;&gt;""),"",DATE(2027,5,7))</f>
+        <v/>
       </c>
       <c r="P27" s="5" t="s">
         <v>50</v>
@@ -7113,14 +7133,15 @@
         <v>212</v>
       </c>
       <c r="M28" s="12">
-        <f ca="1">IF($C28="","",$C28+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A28)="Finalized",$K28&lt;&gt;""),"",IF($C28="","",$C28+365-TODAY()))</f>
         <v>252</v>
       </c>
       <c r="N28" s="12">
-        <f ca="1">IF($C28="","",$C28+120-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A28)="Finalized",$K28&lt;&gt;""),"",IF($C28="","",$C28+120-TODAY()))</f>
         <v>7</v>
       </c>
       <c r="O28" s="6">
+        <f>IF(AND(TRIM($A28)="Finalized",$K28&lt;&gt;""),"",DATE(2027,5,8))</f>
         <v>46515</v>
       </c>
       <c r="P28" s="5" t="s">
@@ -7219,20 +7240,21 @@
       <c r="K29" s="3">
         <v>46252</v>
       </c>
-      <c r="L29" s="12">
+      <c t="str" r="L29" s="12">
         <f ca="1">IF($O29="","",$O29-TODAY())</f>
-        <v>212</v>
-      </c>
-      <c r="M29" s="12">
-        <f ca="1">IF($C29="","",$C29+365-TODAY())</f>
-        <v>258</v>
-      </c>
-      <c r="N29" s="12">
-        <f ca="1">IF($C29="","",$C29+120-TODAY())</f>
-        <v>13</v>
-      </c>
-      <c r="O29" s="6">
-        <v>46515</v>
+        <v/>
+      </c>
+      <c t="str" r="M29" s="12">
+        <f ca="1">IF(AND(TRIM($A29)="Finalized",$K29&lt;&gt;""),"",IF($C29="","",$C29+365-TODAY()))</f>
+        <v/>
+      </c>
+      <c t="str" r="N29" s="12">
+        <f ca="1">IF(AND(TRIM($A29)="Finalized",$K29&lt;&gt;""),"",IF($C29="","",$C29+120-TODAY()))</f>
+        <v/>
+      </c>
+      <c t="str" r="O29" s="6">
+        <f>IF(AND(TRIM($A29)="Finalized",$K29&lt;&gt;""),"",DATE(2027,5,8))</f>
+        <v/>
       </c>
       <c r="P29" s="5" t="s">
         <v>50</v>
@@ -7332,20 +7354,21 @@
       <c r="K30" s="3">
         <v>46245</v>
       </c>
-      <c r="L30" s="12">
+      <c t="str" r="L30" s="12">
         <f ca="1">IF($O30="","",$O30-TODAY())</f>
-        <v>-59</v>
-      </c>
-      <c r="M30" s="12">
-        <f ca="1">IF($F30="","",$F30+90-TODAY())</f>
-        <v>-59</v>
-      </c>
-      <c r="N30" s="12">
-        <f ca="1">IF($C30="","",$C30+365-TODAY())</f>
-        <v>278</v>
-      </c>
-      <c r="O30" s="6">
-        <v>46244</v>
+        <v/>
+      </c>
+      <c t="str" r="M30" s="12">
+        <f ca="1">IF(AND(TRIM($A30)="Finalized",$K30&lt;&gt;""),"",IF($F30="","",$F30+90-TODAY()))</f>
+        <v/>
+      </c>
+      <c t="str" r="N30" s="12">
+        <f ca="1">IF(AND(TRIM($A30)="Finalized",$K30&lt;&gt;""),"",IF($C30="","",$C30+365-TODAY()))</f>
+        <v/>
+      </c>
+      <c t="str" r="O30" s="6">
+        <f>IF(AND(TRIM($A30)="Finalized",$K30&lt;&gt;""),"",DATE(2026,8,10))</f>
+        <v/>
       </c>
       <c r="P30" s="5" t="s">
         <v>46</v>
@@ -7443,7 +7466,7 @@
       <c r="K31" s="3">
         <v>46262</v>
       </c>
-      <c r="L31" s="4" t="str">
+      <c t="str" r="L31" s="4">
         <f ca="1">IF($O31="","",$O31-TODAY())</f>
         <v/>
       </c>
@@ -7502,83 +7525,88 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:AN31" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
+  <conditionalFormatting sqref="L2:O1000">
+    <cfRule type="expression" dxfId="96" priority="1" stopIfTrue="1">
+      <formula>AND(TRIM($A2)="Finalized",$K2&lt;&gt;"")</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="L2:L31 O2:U31">
-    <cfRule type="expression" dxfId="94" priority="1">
+    <cfRule type="expression" dxfId="94" priority="2">
       <formula>AND($L2&lt;&gt;"", $L2&gt;=0, $L2&lt;=5)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="93" priority="2">
+    <cfRule type="expression" dxfId="93" priority="3">
       <formula>AND($L2&lt;&gt;"", $L2&gt;5, $L2&lt;=30)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="92" priority="3">
+    <cfRule type="expression" dxfId="92" priority="4">
       <formula>AND($L2&lt;&gt;"", $L2&gt;30)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="91" priority="4">
+    <cfRule type="expression" dxfId="91" priority="5">
       <formula>AND($L2&lt;&gt;"", $L2&lt;0)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="90" priority="5">
+    <cfRule type="expression" dxfId="90" priority="6">
       <formula>$L2=""</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M2:M31">
-    <cfRule type="expression" dxfId="89" priority="6">
+    <cfRule type="expression" dxfId="89" priority="7">
       <formula>AND($M2&lt;&gt;"", $M2&gt;=0, $M2&lt;=5)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="88" priority="7">
+    <cfRule type="expression" dxfId="88" priority="8">
       <formula>AND($M2&lt;&gt;"", $M2&gt;5, $M2&lt;=30)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="87" priority="8">
+    <cfRule type="expression" dxfId="87" priority="9">
       <formula>AND($M2&lt;&gt;"", $M2&gt;30)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="86" priority="9">
+    <cfRule type="expression" dxfId="86" priority="10">
       <formula>AND($M2&lt;&gt;"", $M2&lt;0)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="85" priority="10">
+    <cfRule type="expression" dxfId="85" priority="11">
       <formula>$M2=""</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N2:N31">
-    <cfRule type="expression" dxfId="84" priority="11">
+    <cfRule type="expression" dxfId="84" priority="12">
       <formula>AND($N2&lt;&gt;"", $N2&gt;=0, $N2&lt;=5)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="83" priority="12">
+    <cfRule type="expression" dxfId="83" priority="13">
       <formula>AND($N2&lt;&gt;"", $N2&gt;5, $N2&lt;=30)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="82" priority="13">
+    <cfRule type="expression" dxfId="82" priority="14">
       <formula>AND($N2&lt;&gt;"", $N2&gt;30)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="81" priority="14">
+    <cfRule type="expression" dxfId="81" priority="15">
       <formula>AND($N2&lt;&gt;"", $N2&lt;0)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="80" priority="15">
+    <cfRule type="expression" dxfId="80" priority="16">
       <formula>$N2=""</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A2:AN1000">
-    <cfRule type="expression" dxfId="95" priority="16">
+    <cfRule type="expression" dxfId="95" priority="17">
       <formula>TRIM($A2)="PAID"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="96" priority="17">
+    <cfRule type="expression" dxfId="96" priority="18">
       <formula>TRIM($A2)="Finalized"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="97" priority="18">
+    <cfRule type="expression" dxfId="97" priority="19">
       <formula>TRIM($A2)="Received"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="98" priority="19">
+    <cfRule type="expression" dxfId="98" priority="20">
       <formula>TRIM($A2)="Pending"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="99" priority="20">
+    <cfRule type="expression" dxfId="99" priority="21">
       <formula>TRIM($A2)="Under Review"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="100" priority="21">
+    <cfRule type="expression" dxfId="100" priority="22">
       <formula>AND(TRIM($A2)="Denied",$K2="")</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="103" priority="24">
+    <cfRule type="expression" dxfId="103" priority="25">
       <formula>AND(TRIM($A2)="Denied",$K2&lt;&gt;"")</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="101" priority="22">
+    <cfRule type="expression" dxfId="101" priority="23">
       <formula>TRIM($A2)="Rejected"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="102" priority="23">
+    <cfRule type="expression" dxfId="102" priority="24">
       <formula>TRIM($A2)="Not found"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -7793,14 +7821,15 @@
         <v>37</v>
       </c>
       <c r="M2" s="12">
-        <f ca="1">IF($F2="","",$F2+180-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A2)="Finalized",$K2&lt;&gt;""),"",IF($F2="","",$F2+180-TODAY()))</f>
         <v>37</v>
       </c>
       <c r="N2" s="12">
-        <f ca="1">IF($C2="","",$C2+180-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A2)="Finalized",$K2&lt;&gt;""),"",IF($C2="","",$C2+180-TODAY()))</f>
         <v>67</v>
       </c>
       <c r="O2" s="6">
+        <f>IF(AND(TRIM($A2)="Finalized",$K2&lt;&gt;""),"",DATE(2026,11,14))</f>
         <v>46340</v>
       </c>
       <c r="P2" s="5" t="s">
@@ -7906,14 +7935,15 @@
         <v>209</v>
       </c>
       <c r="M3" s="12">
-        <f ca="1">IF($C3="","",$C3+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A3)="Finalized",$K3&lt;&gt;""),"",IF($C3="","",$C3+365-TODAY()))</f>
         <v>311</v>
       </c>
       <c r="N3" s="12">
-        <f ca="1">IF($C3="","",$C3+120-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A3)="Finalized",$K3&lt;&gt;""),"",IF($C3="","",$C3+120-TODAY()))</f>
         <v>66</v>
       </c>
       <c r="O3" s="6">
+        <f>IF(AND(TRIM($A3)="Finalized",$K3&lt;&gt;""),"",DATE(2027,5,5))</f>
         <v>46512</v>
       </c>
       <c r="P3" s="5" t="s">
@@ -8019,14 +8049,15 @@
         <v>212</v>
       </c>
       <c r="M4" s="12">
-        <f ca="1">IF($C4="","",$C4+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A4)="Finalized",$K4&lt;&gt;""),"",IF($C4="","",$C4+365-TODAY()))</f>
         <v>264</v>
       </c>
       <c r="N4" s="12">
-        <f ca="1">IF($C4="","",$C4+120-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A4)="Finalized",$K4&lt;&gt;""),"",IF($C4="","",$C4+120-TODAY()))</f>
         <v>19</v>
       </c>
       <c r="O4" s="6">
+        <f>IF(AND(TRIM($A4)="Finalized",$K4&lt;&gt;""),"",DATE(2027,5,8))</f>
         <v>46515</v>
       </c>
       <c r="P4" s="5" t="s">
@@ -8134,14 +8165,15 @@
         <v>230</v>
       </c>
       <c r="M5" s="12">
-        <f ca="1">IF($C5="","",$C5+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A5)="Finalized",$K5&lt;&gt;""),"",IF($C5="","",$C5+365-TODAY()))</f>
         <v>271</v>
       </c>
       <c r="N5" s="12">
-        <f ca="1">IF($C5="","",$C5+120-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A5)="Finalized",$K5&lt;&gt;""),"",IF($C5="","",$C5+120-TODAY()))</f>
         <v>26</v>
       </c>
       <c r="O5" s="6">
+        <f>IF(AND(TRIM($A5)="Finalized",$K5&lt;&gt;""),"",DATE(2027,5,26))</f>
         <v>46533</v>
       </c>
       <c r="P5" s="5" t="s">
@@ -8247,14 +8279,15 @@
         <v>230</v>
       </c>
       <c r="M6" s="12">
-        <f ca="1">IF($C6="","",$C6+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A6)="Finalized",$K6&lt;&gt;""),"",IF($C6="","",$C6+365-TODAY()))</f>
         <v>311</v>
       </c>
       <c r="N6" s="12">
-        <f ca="1">IF($C6="","",$C6+120-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A6)="Finalized",$K6&lt;&gt;""),"",IF($C6="","",$C6+120-TODAY()))</f>
         <v>66</v>
       </c>
       <c r="O6" s="6">
+        <f>IF(AND(TRIM($A6)="Finalized",$K6&lt;&gt;""),"",DATE(2027,5,26))</f>
         <v>46533</v>
       </c>
       <c r="P6" s="5" t="s">
@@ -8356,14 +8389,15 @@
         <v>-70</v>
       </c>
       <c r="M7" s="12" t="str">
-        <f ca="1">IF($C7="","",$C7+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A7)="Finalized",$K7&lt;&gt;""),"",IF($C7="","",$C7+365-TODAY()))</f>
         <v/>
       </c>
       <c r="N7" s="12" t="str">
-        <f ca="1">IF($C7="","",$C7+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A7)="Finalized",$K7&lt;&gt;""),"",IF($C7="","",$C7+365-TODAY()))</f>
         <v/>
       </c>
       <c r="O7" s="6">
+        <f>IF(AND(TRIM($A7)="Finalized",$K7&lt;&gt;""),"",DATE(2026,7,30))</f>
         <v>46233</v>
       </c>
       <c r="P7" s="5" t="s">
@@ -8467,14 +8501,15 @@
         <v>-56</v>
       </c>
       <c r="M8" s="12" t="str">
-        <f ca="1">IF($C8="","",$C8+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A8)="Finalized",$K8&lt;&gt;""),"",IF($C8="","",$C8+365-TODAY()))</f>
         <v/>
       </c>
       <c r="N8" s="12" t="str">
-        <f ca="1">IF($C8="","",$C8+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A8)="Finalized",$K8&lt;&gt;""),"",IF($C8="","",$C8+365-TODAY()))</f>
         <v/>
       </c>
       <c r="O8" s="6">
+        <f>IF(AND(TRIM($A8)="Finalized",$K8&lt;&gt;""),"",DATE(2026,8,13))</f>
         <v>46247</v>
       </c>
       <c r="P8" s="5" t="s">
@@ -8584,14 +8619,15 @@
         <v>-53</v>
       </c>
       <c r="M9" s="12">
-        <f ca="1">IF($C9="","",$C9+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A9)="Finalized",$K9&lt;&gt;""),"",IF($C9="","",$C9+365-TODAY()))</f>
         <v>258</v>
       </c>
       <c r="N9" s="12">
-        <f ca="1">IF($C9="","",$C9+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A9)="Finalized",$K9&lt;&gt;""),"",IF($C9="","",$C9+365-TODAY()))</f>
         <v>258</v>
       </c>
       <c r="O9" s="6">
+        <f>IF(AND(TRIM($A9)="Finalized",$K9&lt;&gt;""),"",DATE(2026,8,16))</f>
         <v>46250</v>
       </c>
       <c r="P9" s="5" t="s">
@@ -8697,14 +8733,15 @@
         <v>-53</v>
       </c>
       <c r="M10" s="12">
-        <f ca="1">IF($F10="","",$F10+90-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A10)="Finalized",$K10&lt;&gt;""),"",IF($F10="","",$F10+90-TODAY()))</f>
         <v>-53</v>
       </c>
       <c r="N10" s="12">
-        <f ca="1">IF($C10="","",$C10+540-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A10)="Finalized",$K10&lt;&gt;""),"",IF($C10="","",$C10+540-TODAY()))</f>
         <v>422</v>
       </c>
       <c r="O10" s="6">
+        <f>IF(AND(TRIM($A10)="Finalized",$K10&lt;&gt;""),"",DATE(2026,8,16))</f>
         <v>46250</v>
       </c>
       <c r="P10" s="5" t="s">
@@ -8812,14 +8849,15 @@
         <v>-22</v>
       </c>
       <c r="M11" s="12">
-        <f ca="1">IF($C11="","",$C11+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A11)="Finalized",$K11&lt;&gt;""),"",IF($C11="","",$C11+365-TODAY()))</f>
         <v>246</v>
       </c>
       <c r="N11" s="12">
-        <f ca="1">IF($C11="","",$C11+90-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A11)="Finalized",$K11&lt;&gt;""),"",IF($C11="","",$C11+90-TODAY()))</f>
         <v>-29</v>
       </c>
       <c r="O11" s="6">
+        <f>IF(AND(TRIM($A11)="Finalized",$K11&lt;&gt;""),"",DATE(2026,9,16))</f>
         <v>46281</v>
       </c>
       <c r="P11" s="5" t="s">
@@ -8927,14 +8965,15 @@
         <v>-15</v>
       </c>
       <c r="M12" s="12">
-        <f ca="1">IF($F12="","",$F12+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A12)="Finalized",$K12&lt;&gt;""),"",IF($F12="","",$F12+365-TODAY()))</f>
         <v>230</v>
       </c>
       <c r="N12" s="12">
-        <f ca="1">IF($F12="","",$F12+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A12)="Finalized",$K12&lt;&gt;""),"",IF($F12="","",$F12+365-TODAY()))</f>
         <v>230</v>
       </c>
       <c r="O12" s="6">
+        <f>IF(AND(TRIM($A12)="Finalized",$K12&lt;&gt;""),"",DATE(2026,9,23))</f>
         <v>46288</v>
       </c>
       <c r="P12" s="5" t="s">
@@ -9046,14 +9085,15 @@
         <v>23</v>
       </c>
       <c r="M13" s="12">
-        <f ca="1">IF($F13="","",$F13+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A13)="Finalized",$K13&lt;&gt;""),"",IF($F13="","",$F13+365-TODAY()))</f>
         <v>208</v>
       </c>
       <c r="N13" s="12">
-        <f ca="1">IF($F13="","",$F13+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A13)="Finalized",$K13&lt;&gt;""),"",IF($F13="","",$F13+365-TODAY()))</f>
         <v>208</v>
       </c>
       <c r="O13" s="6">
+        <f>IF(AND(TRIM($A13)="Finalized",$K13&lt;&gt;""),"",DATE(2026,10,31))</f>
         <v>46326</v>
       </c>
       <c r="P13" s="5" t="s">
@@ -9161,14 +9201,15 @@
         <v>47</v>
       </c>
       <c r="M14" s="12">
-        <f ca="1">IF($F14="","",$F14+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A14)="Finalized",$K14&lt;&gt;""),"",IF($F14="","",$F14+365-TODAY()))</f>
         <v>232</v>
       </c>
       <c r="N14" s="12">
-        <f ca="1">IF($F14="","",$F14+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A14)="Finalized",$K14&lt;&gt;""),"",IF($F14="","",$F14+365-TODAY()))</f>
         <v>232</v>
       </c>
       <c r="O14" s="6">
+        <f>IF(AND(TRIM($A14)="Finalized",$K14&lt;&gt;""),"",DATE(2026,11,24))</f>
         <v>46350</v>
       </c>
       <c r="P14" s="5" t="s">
@@ -9278,14 +9319,15 @@
         <v>209</v>
       </c>
       <c r="M15" s="12">
-        <f ca="1">IF($C15="","",$C15+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A15)="Finalized",$K15&lt;&gt;""),"",IF($C15="","",$C15+365-TODAY()))</f>
         <v>218</v>
       </c>
       <c r="N15" s="12">
-        <f ca="1">IF($C15="","",$C15+120-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A15)="Finalized",$K15&lt;&gt;""),"",IF($C15="","",$C15+120-TODAY()))</f>
         <v>-27</v>
       </c>
       <c r="O15" s="6">
+        <f>IF(AND(TRIM($A15)="Finalized",$K15&lt;&gt;""),"",DATE(2027,5,5))</f>
         <v>46512</v>
       </c>
       <c r="P15" s="5" t="s">
@@ -9391,14 +9433,15 @@
         <v>212</v>
       </c>
       <c r="M16" s="12">
-        <f ca="1">IF($C16="","",$C16+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A16)="Finalized",$K16&lt;&gt;""),"",IF($C16="","",$C16+365-TODAY()))</f>
         <v>247</v>
       </c>
       <c r="N16" s="12">
-        <f ca="1">IF($C16="","",$C16+120-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A16)="Finalized",$K16&lt;&gt;""),"",IF($C16="","",$C16+120-TODAY()))</f>
         <v>2</v>
       </c>
       <c r="O16" s="6">
+        <f>IF(AND(TRIM($A16)="Finalized",$K16&lt;&gt;""),"",DATE(2027,5,8))</f>
         <v>46515</v>
       </c>
       <c r="P16" s="5" t="s">
@@ -9508,14 +9551,15 @@
         <v>218</v>
       </c>
       <c r="M17" s="12">
-        <f ca="1">IF($C17="","",$C17+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A17)="Finalized",$K17&lt;&gt;""),"",IF($C17="","",$C17+365-TODAY()))</f>
         <v>273</v>
       </c>
       <c r="N17" s="12">
-        <f ca="1">IF($C17="","",$C17+120-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A17)="Finalized",$K17&lt;&gt;""),"",IF($C17="","",$C17+120-TODAY()))</f>
         <v>28</v>
       </c>
       <c r="O17" s="6">
+        <f>IF(AND(TRIM($A17)="Finalized",$K17&lt;&gt;""),"",DATE(2027,5,14))</f>
         <v>46521</v>
       </c>
       <c r="P17" s="5" t="s">
@@ -9625,14 +9669,15 @@
         <v>232</v>
       </c>
       <c r="M18" s="12">
-        <f ca="1">IF($C18="","",$C18+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A18)="Finalized",$K18&lt;&gt;""),"",IF($C18="","",$C18+365-TODAY()))</f>
         <v>266</v>
       </c>
       <c r="N18" s="12">
-        <f ca="1">IF($C18="","",$C18+120-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A18)="Finalized",$K18&lt;&gt;""),"",IF($C18="","",$C18+120-TODAY()))</f>
         <v>21</v>
       </c>
       <c r="O18" s="6">
+        <f>IF(AND(TRIM($A18)="Finalized",$K18&lt;&gt;""),"",DATE(2027,5,28))</f>
         <v>46535</v>
       </c>
       <c r="P18" s="5" t="s">
@@ -9744,14 +9789,15 @@
         <v>-90</v>
       </c>
       <c r="M19" s="12">
-        <f ca="1">IF($C19="","",$C19+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A19)="Finalized",$K19&lt;&gt;""),"",IF($C19="","",$C19+365-TODAY()))</f>
         <v>224</v>
       </c>
       <c r="N19" s="12">
-        <f ca="1">IF($C19="","",$C19+90-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A19)="Finalized",$K19&lt;&gt;""),"",IF($C19="","",$C19+90-TODAY()))</f>
         <v>-51</v>
       </c>
       <c r="O19" s="6">
+        <f>IF(AND(TRIM($A19)="Finalized",$K19&lt;&gt;""),"",DATE(2026,7,10))</f>
         <v>46213</v>
       </c>
       <c r="P19" s="5" t="s">
@@ -9857,14 +9903,15 @@
         <v>-67</v>
       </c>
       <c r="M20" s="12">
-        <f ca="1">IF($F20="","",$F20+90-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A20)="Finalized",$K20&lt;&gt;""),"",IF($F20="","",$F20+90-TODAY()))</f>
         <v>-67</v>
       </c>
       <c r="N20" s="12">
-        <f ca="1">IF($C20="","",$C20+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A20)="Finalized",$K20&lt;&gt;""),"",IF($C20="","",$C20+365-TODAY()))</f>
         <v>246</v>
       </c>
       <c r="O20" s="6">
+        <f>IF(AND(TRIM($A20)="Finalized",$K20&lt;&gt;""),"",DATE(2026,8,2))</f>
         <v>46236</v>
       </c>
       <c r="P20" s="5" t="s">
@@ -9972,14 +10019,15 @@
         <v>-63</v>
       </c>
       <c r="M21" s="12">
-        <f ca="1">IF($F21="","",$F21+90-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A21)="Finalized",$K21&lt;&gt;""),"",IF($F21="","",$F21+90-TODAY()))</f>
         <v>-63</v>
       </c>
       <c r="N21" s="12">
-        <f ca="1">IF($C21="","",$C21+180-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A21)="Finalized",$K21&lt;&gt;""),"",IF($C21="","",$C21+180-TODAY()))</f>
         <v>101</v>
       </c>
       <c r="O21" s="6">
+        <f>IF(AND(TRIM($A21)="Finalized",$K21&lt;&gt;""),"",DATE(2026,8,6))</f>
         <v>46240</v>
       </c>
       <c r="P21" s="5" t="s">
@@ -10087,14 +10135,15 @@
         <v>-60</v>
       </c>
       <c r="M22" s="12">
-        <f ca="1">IF($F22="","",$F22+90-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A22)="Finalized",$K22&lt;&gt;""),"",IF($F22="","",$F22+90-TODAY()))</f>
         <v>-60</v>
       </c>
       <c r="N22" s="12">
-        <f ca="1">IF($C22="","",$C22+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A22)="Finalized",$K22&lt;&gt;""),"",IF($C22="","",$C22+365-TODAY()))</f>
         <v>265</v>
       </c>
       <c r="O22" s="6">
+        <f>IF(AND(TRIM($A22)="Finalized",$K22&lt;&gt;""),"",DATE(2026,8,9))</f>
         <v>46243</v>
       </c>
       <c r="P22" s="5" t="s">
@@ -10389,20 +10438,21 @@
       <c r="K25" s="3">
         <v>46245</v>
       </c>
-      <c r="L25" s="12">
+      <c t="str" r="L25" s="12">
         <f ca="1">IF($O25="","",$O25-TODAY())</f>
-        <v>-50</v>
-      </c>
-      <c r="M25" s="12">
-        <f ca="1">IF($C25="","",$C25+180-TODAY())</f>
-        <v>60</v>
-      </c>
-      <c r="N25" s="12">
-        <f ca="1">IF($C25="","",$C25+365-TODAY())</f>
-        <v>245</v>
-      </c>
-      <c r="O25" s="6">
-        <v>46253</v>
+        <v/>
+      </c>
+      <c t="str" r="M25" s="12">
+        <f ca="1">IF(AND(TRIM($A25)="Finalized",$K25&lt;&gt;""),"",IF($C25="","",$C25+180-TODAY()))</f>
+        <v/>
+      </c>
+      <c t="str" r="N25" s="12">
+        <f ca="1">IF(AND(TRIM($A25)="Finalized",$K25&lt;&gt;""),"",IF($C25="","",$C25+365-TODAY()))</f>
+        <v/>
+      </c>
+      <c t="str" r="O25" s="6">
+        <f>IF(AND(TRIM($A25)="Finalized",$K25&lt;&gt;""),"",DATE(2026,8,19))</f>
+        <v/>
       </c>
       <c r="P25" s="5" t="s">
         <v>46</v>
@@ -10504,20 +10554,21 @@
       <c r="K26" s="3">
         <v>46245</v>
       </c>
-      <c r="L26" s="12">
+      <c t="str" r="L26" s="12">
         <f ca="1">IF($O26="","",$O26-TODAY())</f>
-        <v>-49</v>
-      </c>
-      <c r="M26" s="12">
-        <f ca="1">IF($C26="","",$C26+365-TODAY())</f>
-        <v>256</v>
-      </c>
-      <c r="N26" s="12">
-        <f ca="1">IF($C26="","",$C26+365-TODAY())</f>
-        <v>256</v>
-      </c>
-      <c r="O26" s="6">
-        <v>46254</v>
+        <v/>
+      </c>
+      <c t="str" r="M26" s="12">
+        <f ca="1">IF(AND(TRIM($A26)="Finalized",$K26&lt;&gt;""),"",IF($C26="","",$C26+365-TODAY()))</f>
+        <v/>
+      </c>
+      <c t="str" r="N26" s="12">
+        <f ca="1">IF(AND(TRIM($A26)="Finalized",$K26&lt;&gt;""),"",IF($C26="","",$C26+365-TODAY()))</f>
+        <v/>
+      </c>
+      <c t="str" r="O26" s="6">
+        <f>IF(AND(TRIM($A26)="Finalized",$K26&lt;&gt;""),"",DATE(2026,8,20))</f>
+        <v/>
       </c>
       <c r="P26" s="5" t="s">
         <v>46</v>
@@ -10619,20 +10670,21 @@
       <c r="K27" s="3">
         <v>46248</v>
       </c>
-      <c r="L27" s="12">
+      <c t="str" r="L27" s="12">
         <f ca="1">IF($O27="","",$O27-TODAY())</f>
-        <v>-45</v>
-      </c>
-      <c r="M27" s="12">
-        <f ca="1">IF($C27="","",$C27+180-TODAY())</f>
-        <v>68</v>
-      </c>
-      <c r="N27" s="12">
-        <f ca="1">IF($C27="","",$C27+365-TODAY())</f>
-        <v>253</v>
-      </c>
-      <c r="O27" s="6">
-        <v>46258</v>
+        <v/>
+      </c>
+      <c t="str" r="M27" s="12">
+        <f ca="1">IF(AND(TRIM($A27)="Finalized",$K27&lt;&gt;""),"",IF($C27="","",$C27+180-TODAY()))</f>
+        <v/>
+      </c>
+      <c t="str" r="N27" s="12">
+        <f ca="1">IF(AND(TRIM($A27)="Finalized",$K27&lt;&gt;""),"",IF($C27="","",$C27+365-TODAY()))</f>
+        <v/>
+      </c>
+      <c t="str" r="O27" s="6">
+        <f>IF(AND(TRIM($A27)="Finalized",$K27&lt;&gt;""),"",DATE(2026,8,24))</f>
+        <v/>
       </c>
       <c r="P27" s="5" t="s">
         <v>46</v>
@@ -10736,17 +10788,18 @@
       <c r="K28" s="3">
         <v>46248</v>
       </c>
-      <c r="L28" s="12">
+      <c t="str" r="L28" s="12">
         <f ca="1">IF($O28="","",$O28-TODAY())</f>
-        <v>-37</v>
+        <v/>
       </c>
       <c r="M28" s="12"/>
-      <c r="N28" s="12">
-        <f ca="1">IF($C28="","",$C28+65-TODAY())</f>
-        <v>-15</v>
-      </c>
-      <c r="O28" s="6">
-        <v>46266</v>
+      <c t="str" r="N28" s="12">
+        <f ca="1">IF(AND(TRIM($A28)="Finalized",$K28&lt;&gt;""),"",IF($C28="","",$C28+65-TODAY()))</f>
+        <v/>
+      </c>
+      <c t="str" r="O28" s="6">
+        <f>IF(AND(TRIM($A28)="Finalized",$K28&lt;&gt;""),"",DATE(2026,9,1))</f>
+        <v/>
       </c>
       <c r="P28" s="5" t="s">
         <v>103</v>
@@ -10842,20 +10895,21 @@
       <c r="K29" s="3">
         <v>46254</v>
       </c>
-      <c r="L29" s="12">
+      <c t="str" r="L29" s="12">
         <f ca="1">IF($O29="","",$O29-TODAY())</f>
-        <v>218</v>
-      </c>
-      <c r="M29" s="12">
-        <f ca="1">IF($C29="","",$C29+365-TODAY())</f>
-        <v>309</v>
-      </c>
-      <c r="N29" s="12">
-        <f ca="1">IF($C29="","",$C29+120-TODAY())</f>
-        <v>64</v>
-      </c>
-      <c r="O29" s="6">
-        <v>46521</v>
+        <v/>
+      </c>
+      <c t="str" r="M29" s="12">
+        <f ca="1">IF(AND(TRIM($A29)="Finalized",$K29&lt;&gt;""),"",IF($C29="","",$C29+365-TODAY()))</f>
+        <v/>
+      </c>
+      <c t="str" r="N29" s="12">
+        <f ca="1">IF(AND(TRIM($A29)="Finalized",$K29&lt;&gt;""),"",IF($C29="","",$C29+120-TODAY()))</f>
+        <v/>
+      </c>
+      <c t="str" r="O29" s="6">
+        <f>IF(AND(TRIM($A29)="Finalized",$K29&lt;&gt;""),"",DATE(2027,5,14))</f>
+        <v/>
       </c>
       <c r="P29" s="5" t="s">
         <v>50</v>
@@ -10957,20 +11011,21 @@
       <c r="K30" s="3">
         <v>46255</v>
       </c>
-      <c r="L30" s="12">
+      <c t="str" r="L30" s="12">
         <f ca="1">IF($O30="","",$O30-TODAY())</f>
-        <v>222</v>
-      </c>
-      <c r="M30" s="12">
-        <f ca="1">IF($C30="","",$C30+365-TODAY())</f>
-        <v>281</v>
-      </c>
-      <c r="N30" s="12">
-        <f ca="1">IF($C30="","",$C30+120-TODAY())</f>
-        <v>36</v>
-      </c>
-      <c r="O30" s="6">
-        <v>46525</v>
+        <v/>
+      </c>
+      <c t="str" r="M30" s="12">
+        <f ca="1">IF(AND(TRIM($A30)="Finalized",$K30&lt;&gt;""),"",IF($C30="","",$C30+365-TODAY()))</f>
+        <v/>
+      </c>
+      <c t="str" r="N30" s="12">
+        <f ca="1">IF(AND(TRIM($A30)="Finalized",$K30&lt;&gt;""),"",IF($C30="","",$C30+120-TODAY()))</f>
+        <v/>
+      </c>
+      <c t="str" r="O30" s="6">
+        <f>IF(AND(TRIM($A30)="Finalized",$K30&lt;&gt;""),"",DATE(2027,5,18))</f>
+        <v/>
       </c>
       <c r="P30" s="5" t="s">
         <v>50</v>
@@ -11070,20 +11125,21 @@
       <c r="K31" s="3">
         <v>46255</v>
       </c>
-      <c r="L31" s="12">
+      <c t="str" r="L31" s="12">
         <f ca="1">IF($O31="","",$O31-TODAY())</f>
-        <v>223</v>
-      </c>
-      <c r="M31" s="12">
-        <f ca="1">IF($C31="","",$C31+365-TODAY())</f>
-        <v>308</v>
-      </c>
-      <c r="N31" s="12">
-        <f ca="1">IF($C31="","",$C31+120-TODAY())</f>
-        <v>63</v>
-      </c>
-      <c r="O31" s="6">
-        <v>46526</v>
+        <v/>
+      </c>
+      <c t="str" r="M31" s="12">
+        <f ca="1">IF(AND(TRIM($A31)="Finalized",$K31&lt;&gt;""),"",IF($C31="","",$C31+365-TODAY()))</f>
+        <v/>
+      </c>
+      <c t="str" r="N31" s="12">
+        <f ca="1">IF(AND(TRIM($A31)="Finalized",$K31&lt;&gt;""),"",IF($C31="","",$C31+120-TODAY()))</f>
+        <v/>
+      </c>
+      <c t="str" r="O31" s="6">
+        <f>IF(AND(TRIM($A31)="Finalized",$K31&lt;&gt;""),"",DATE(2027,5,19))</f>
+        <v/>
       </c>
       <c r="P31" s="5" t="s">
         <v>50</v>
@@ -11185,20 +11241,21 @@
       <c r="K32" s="3">
         <v>46276</v>
       </c>
-      <c r="L32" s="12">
+      <c t="str" r="L32" s="12">
         <f ca="1">IF($O32="","",$O32-TODAY())</f>
-        <v>233</v>
-      </c>
-      <c r="M32" s="12">
-        <f ca="1">IF($C32="","",$C32+365-TODAY())</f>
-        <v>330</v>
-      </c>
-      <c r="N32" s="12">
-        <f ca="1">IF($C32="","",$C32+120-TODAY())</f>
-        <v>85</v>
-      </c>
-      <c r="O32" s="6">
-        <v>46536</v>
+        <v/>
+      </c>
+      <c t="str" r="M32" s="12">
+        <f ca="1">IF(AND(TRIM($A32)="Finalized",$K32&lt;&gt;""),"",IF($C32="","",$C32+365-TODAY()))</f>
+        <v/>
+      </c>
+      <c t="str" r="N32" s="12">
+        <f ca="1">IF(AND(TRIM($A32)="Finalized",$K32&lt;&gt;""),"",IF($C32="","",$C32+120-TODAY()))</f>
+        <v/>
+      </c>
+      <c t="str" r="O32" s="6">
+        <f>IF(AND(TRIM($A32)="Finalized",$K32&lt;&gt;""),"",DATE(2027,5,29))</f>
+        <v/>
       </c>
       <c r="P32" s="5" t="s">
         <v>50</v>
@@ -11302,20 +11359,21 @@
       <c r="K33" s="3">
         <v>46253</v>
       </c>
-      <c r="L33" s="12">
+      <c t="str" r="L33" s="12">
         <f ca="1">IF($O33="","",$O33-TODAY())</f>
-        <v>-70</v>
-      </c>
-      <c r="M33" s="12">
-        <f ca="1">IF($C33="","",$C33+180-TODAY())</f>
-        <v>47</v>
-      </c>
-      <c r="N33" s="12">
-        <f ca="1">IF($C33="","",$C33+365-TODAY())</f>
-        <v>232</v>
-      </c>
-      <c r="O33" s="6">
-        <v>46233</v>
+        <v/>
+      </c>
+      <c t="str" r="M33" s="12">
+        <f ca="1">IF(AND(TRIM($A33)="Finalized",$K33&lt;&gt;""),"",IF($C33="","",$C33+180-TODAY()))</f>
+        <v/>
+      </c>
+      <c t="str" r="N33" s="12">
+        <f ca="1">IF(AND(TRIM($A33)="Finalized",$K33&lt;&gt;""),"",IF($C33="","",$C33+365-TODAY()))</f>
+        <v/>
+      </c>
+      <c t="str" r="O33" s="6">
+        <f>IF(AND(TRIM($A33)="Finalized",$K33&lt;&gt;""),"",DATE(2026,7,30))</f>
+        <v/>
       </c>
       <c r="P33" s="5" t="s">
         <v>46</v>
@@ -11415,20 +11473,21 @@
       <c r="K34" s="3">
         <v>46253</v>
       </c>
-      <c r="L34" s="12">
+      <c t="str" r="L34" s="12">
         <f ca="1">IF($O34="","",$O34-TODAY())</f>
-        <v>-63</v>
-      </c>
-      <c r="M34" s="12">
-        <f ca="1">IF($C34="","",$C34+180-TODAY())</f>
-        <v>72</v>
-      </c>
-      <c r="N34" s="12">
-        <f ca="1">IF($C34="","",$C34+365-TODAY())</f>
-        <v>257</v>
-      </c>
-      <c r="O34" s="6">
-        <v>46240</v>
+        <v/>
+      </c>
+      <c t="str" r="M34" s="12">
+        <f ca="1">IF(AND(TRIM($A34)="Finalized",$K34&lt;&gt;""),"",IF($C34="","",$C34+180-TODAY()))</f>
+        <v/>
+      </c>
+      <c t="str" r="N34" s="12">
+        <f ca="1">IF(AND(TRIM($A34)="Finalized",$K34&lt;&gt;""),"",IF($C34="","",$C34+365-TODAY()))</f>
+        <v/>
+      </c>
+      <c t="str" r="O34" s="6">
+        <f>IF(AND(TRIM($A34)="Finalized",$K34&lt;&gt;""),"",DATE(2026,8,6))</f>
+        <v/>
       </c>
       <c r="P34" s="5" t="s">
         <v>46</v>
@@ -11534,20 +11593,21 @@
       <c r="K35" s="3">
         <v>46253</v>
       </c>
-      <c r="L35" s="12">
+      <c t="str" r="L35" s="12">
         <f ca="1">IF($O35="","",$O35-TODAY())</f>
-        <v>-60</v>
-      </c>
-      <c r="M35" s="12">
-        <f ca="1">IF($C35="","",$C35+365-TODAY())</f>
-        <v>260</v>
-      </c>
-      <c r="N35" s="12">
-        <f ca="1">IF($C35="","",$C35+365-TODAY())</f>
-        <v>260</v>
-      </c>
-      <c r="O35" s="6">
-        <v>46243</v>
+        <v/>
+      </c>
+      <c t="str" r="M35" s="12">
+        <f ca="1">IF(AND(TRIM($A35)="Finalized",$K35&lt;&gt;""),"",IF($C35="","",$C35+365-TODAY()))</f>
+        <v/>
+      </c>
+      <c t="str" r="N35" s="12">
+        <f ca="1">IF(AND(TRIM($A35)="Finalized",$K35&lt;&gt;""),"",IF($C35="","",$C35+365-TODAY()))</f>
+        <v/>
+      </c>
+      <c t="str" r="O35" s="6">
+        <f>IF(AND(TRIM($A35)="Finalized",$K35&lt;&gt;""),"",DATE(2026,8,9))</f>
+        <v/>
       </c>
       <c r="P35" s="5" t="s">
         <v>46</v>
@@ -11617,100 +11677,105 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:AN35" xr:uid="{00000000-0009-0000-0000-000001000000}"/>
+  <conditionalFormatting sqref="L2:O1000">
+    <cfRule type="expression" dxfId="96" priority="1" stopIfTrue="1">
+      <formula>AND(TRIM($A2)="Finalized",$K2&lt;&gt;"")</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="L2:L35">
-    <cfRule type="expression" dxfId="79" priority="1">
+    <cfRule type="expression" dxfId="79" priority="2">
       <formula>AND($L2&lt;&gt;"", $L2&gt;=0, $L2&lt;=5)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="78" priority="2">
+    <cfRule type="expression" dxfId="78" priority="3">
       <formula>AND($L2&lt;&gt;"", $L2&gt;5, $L2&lt;=30)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="77" priority="3">
+    <cfRule type="expression" dxfId="77" priority="4">
       <formula>AND($L2&lt;&gt;"", $L2&gt;30)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="76" priority="4">
+    <cfRule type="expression" dxfId="76" priority="5">
       <formula>AND($L2&lt;&gt;"", $L2&lt;0)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="75" priority="5">
+    <cfRule type="expression" dxfId="75" priority="6">
       <formula>$L2=""</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M2:M35">
-    <cfRule type="expression" dxfId="74" priority="6">
+    <cfRule type="expression" dxfId="74" priority="7">
       <formula>AND($M2&lt;&gt;"", $M2&gt;=0, $M2&lt;=5)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="73" priority="7">
+    <cfRule type="expression" dxfId="73" priority="8">
       <formula>AND($M2&lt;&gt;"", $M2&gt;5, $M2&lt;=30)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="72" priority="8">
+    <cfRule type="expression" dxfId="72" priority="9">
       <formula>AND($M2&lt;&gt;"", $M2&gt;30)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="71" priority="9">
+    <cfRule type="expression" dxfId="71" priority="10">
       <formula>AND($M2&lt;&gt;"", $M2&lt;0)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="70" priority="10">
+    <cfRule type="expression" dxfId="70" priority="11">
       <formula>$M2=""</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N2:N35">
-    <cfRule type="expression" dxfId="69" priority="11">
+    <cfRule type="expression" dxfId="69" priority="12">
       <formula>AND($N2&lt;&gt;"", $N2&gt;=0, $N2&lt;=5)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="68" priority="12">
+    <cfRule type="expression" dxfId="68" priority="13">
       <formula>AND($N2&lt;&gt;"", $N2&gt;5, $N2&lt;=30)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="67" priority="13">
+    <cfRule type="expression" dxfId="67" priority="14">
       <formula>AND($N2&lt;&gt;"", $N2&gt;30)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="66" priority="14">
+    <cfRule type="expression" dxfId="66" priority="15">
       <formula>AND($N2&lt;&gt;"", $N2&lt;0)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="65" priority="15">
+    <cfRule type="expression" dxfId="65" priority="16">
       <formula>$N2=""</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="O2:U35">
-    <cfRule type="expression" dxfId="64" priority="16">
+    <cfRule type="expression" dxfId="64" priority="17">
       <formula>AND($L2&lt;&gt;"", $L2&gt;=0, $L2&lt;=5)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="63" priority="17">
+    <cfRule type="expression" dxfId="63" priority="18">
       <formula>AND($L2&lt;&gt;"", $L2&gt;5, $L2&lt;=30)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="62" priority="18">
+    <cfRule type="expression" dxfId="62" priority="19">
       <formula>AND($L2&lt;&gt;"", $L2&gt;30)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="61" priority="19">
+    <cfRule type="expression" dxfId="61" priority="20">
       <formula>AND($L2&lt;&gt;"", $L2&lt;0)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="60" priority="20">
+    <cfRule type="expression" dxfId="60" priority="21">
       <formula>$L2=""</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A2:AN1000">
-    <cfRule type="expression" dxfId="95" priority="21">
+    <cfRule type="expression" dxfId="95" priority="22">
       <formula>TRIM($A2)="PAID"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="96" priority="22">
+    <cfRule type="expression" dxfId="96" priority="23">
       <formula>TRIM($A2)="Finalized"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="97" priority="23">
+    <cfRule type="expression" dxfId="97" priority="24">
       <formula>TRIM($A2)="Received"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="98" priority="24">
+    <cfRule type="expression" dxfId="98" priority="25">
       <formula>TRIM($A2)="Pending"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="99" priority="25">
+    <cfRule type="expression" dxfId="99" priority="26">
       <formula>TRIM($A2)="Under Review"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="100" priority="26">
+    <cfRule type="expression" dxfId="100" priority="27">
       <formula>AND(TRIM($A2)="Denied",$K2="")</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="103" priority="29">
+    <cfRule type="expression" dxfId="103" priority="30">
       <formula>AND(TRIM($A2)="Denied",$K2&lt;&gt;"")</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="101" priority="27">
+    <cfRule type="expression" dxfId="101" priority="28">
       <formula>TRIM($A2)="Rejected"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="102" priority="28">
+    <cfRule type="expression" dxfId="102" priority="29">
       <formula>TRIM($A2)="Not found"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -12024,14 +12089,15 @@
         <v>215</v>
       </c>
       <c r="M3" s="12">
-        <f ca="1">IF($C3="","",$C3+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A3)="Finalized",$K3&lt;&gt;""),"",IF($C3="","",$C3+365-TODAY()))</f>
         <v>247</v>
       </c>
       <c r="N3" s="12">
-        <f ca="1">IF($C3="","",$C3+120-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A3)="Finalized",$K3&lt;&gt;""),"",IF($C3="","",$C3+120-TODAY()))</f>
         <v>2</v>
       </c>
       <c r="O3" s="6">
+        <f>IF(AND(TRIM($A3)="Finalized",$K3&lt;&gt;""),"",DATE(2027,5,11))</f>
         <v>46518</v>
       </c>
       <c r="P3" s="5" t="s">
@@ -12145,14 +12211,15 @@
         <v>-60</v>
       </c>
       <c r="M4" s="12">
-        <f ca="1">IF($F4="","",$F4+90-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A4)="Finalized",$K4&lt;&gt;""),"",IF($F4="","",$F4+90-TODAY()))</f>
         <v>-60</v>
       </c>
       <c r="N4" s="12">
-        <f ca="1">IF($C4="","",$C4+540-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A4)="Finalized",$K4&lt;&gt;""),"",IF($C4="","",$C4+540-TODAY()))</f>
         <v>433</v>
       </c>
       <c r="O4" s="6">
+        <f>IF(AND(TRIM($A4)="Finalized",$K4&lt;&gt;""),"",DATE(2026,8,9))</f>
         <v>46243</v>
       </c>
       <c r="P4" s="5" t="s">
@@ -12261,20 +12328,21 @@
       <c r="K5" s="3">
         <v>46248</v>
       </c>
-      <c r="L5" s="12">
+      <c t="str" r="L5" s="12">
         <f ca="1">IF($O5="","",$O5-TODAY())</f>
-        <v>-37</v>
-      </c>
-      <c r="M5" s="12">
-        <f ca="1">IF($C5="","",$C5+180-TODAY())</f>
-        <v>72</v>
-      </c>
-      <c r="N5" s="12">
-        <f ca="1">IF($C5="","",$C5+180-TODAY())</f>
-        <v>72</v>
-      </c>
-      <c r="O5" s="6">
-        <v>46266</v>
+        <v/>
+      </c>
+      <c t="str" r="M5" s="12">
+        <f ca="1">IF(AND(TRIM($A5)="Finalized",$K5&lt;&gt;""),"",IF($C5="","",$C5+180-TODAY()))</f>
+        <v/>
+      </c>
+      <c t="str" r="N5" s="12">
+        <f ca="1">IF(AND(TRIM($A5)="Finalized",$K5&lt;&gt;""),"",IF($C5="","",$C5+180-TODAY()))</f>
+        <v/>
+      </c>
+      <c t="str" r="O5" s="6">
+        <f>IF(AND(TRIM($A5)="Finalized",$K5&lt;&gt;""),"",DATE(2026,9,1))</f>
+        <v/>
       </c>
       <c r="P5" s="5" t="s">
         <v>103</v>
@@ -12383,14 +12451,15 @@
         <v>222</v>
       </c>
       <c r="M6" s="12">
-        <f ca="1">IF($C6="","",$C6+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A6)="Finalized",$K6&lt;&gt;""),"",IF($C6="","",$C6+365-TODAY()))</f>
         <v>314</v>
       </c>
       <c r="N6" s="12">
-        <f ca="1">IF($C6="","",$C6+120-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A6)="Finalized",$K6&lt;&gt;""),"",IF($C6="","",$C6+120-TODAY()))</f>
         <v>69</v>
       </c>
       <c r="O6" s="6">
+        <f>IF(AND(TRIM($A6)="Finalized",$K6&lt;&gt;""),"",DATE(2027,5,18))</f>
         <v>46525</v>
       </c>
       <c r="P6" s="5" t="s">
@@ -12501,20 +12570,21 @@
       <c r="K7" s="3">
         <v>46255</v>
       </c>
-      <c r="L7" s="12">
+      <c t="str" r="L7" s="12">
         <f ca="1">IF($O7="","",$O7-TODAY())</f>
-        <v>-60</v>
-      </c>
-      <c r="M7" s="12">
-        <f ca="1">IF($F7="","",$F7+90-TODAY())</f>
-        <v>-60</v>
-      </c>
-      <c r="N7" s="12">
-        <f ca="1">IF($C7="","",$C7+60-TODAY())</f>
-        <v>-56</v>
-      </c>
-      <c r="O7" s="6">
-        <v>46243</v>
+        <v/>
+      </c>
+      <c t="str" r="M7" s="12">
+        <f ca="1">IF(AND(TRIM($A7)="Finalized",$K7&lt;&gt;""),"",IF($F7="","",$F7+90-TODAY()))</f>
+        <v/>
+      </c>
+      <c t="str" r="N7" s="12">
+        <f ca="1">IF(AND(TRIM($A7)="Finalized",$K7&lt;&gt;""),"",IF($C7="","",$C7+60-TODAY()))</f>
+        <v/>
+      </c>
+      <c t="str" r="O7" s="6">
+        <f>IF(AND(TRIM($A7)="Finalized",$K7&lt;&gt;""),"",DATE(2026,8,9))</f>
+        <v/>
       </c>
       <c r="P7" s="5" t="s">
         <v>46</v>
@@ -12588,100 +12658,105 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:AN7" xr:uid="{00000000-0009-0000-0000-000002000000}"/>
+  <conditionalFormatting sqref="L2:O1000">
+    <cfRule type="expression" dxfId="96" priority="1" stopIfTrue="1">
+      <formula>AND(TRIM($A2)="Finalized",$K2&lt;&gt;"")</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="L2:L7">
-    <cfRule type="expression" dxfId="59" priority="1">
+    <cfRule type="expression" dxfId="59" priority="2">
       <formula>AND($L2&lt;&gt;"", $L2&gt;=0, $L2&lt;=5)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="58" priority="2">
+    <cfRule type="expression" dxfId="58" priority="3">
       <formula>AND($L2&lt;&gt;"", $L2&gt;5, $L2&lt;=30)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="57" priority="3">
+    <cfRule type="expression" dxfId="57" priority="4">
       <formula>AND($L2&lt;&gt;"", $L2&gt;30)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="56" priority="4">
+    <cfRule type="expression" dxfId="56" priority="5">
       <formula>AND($L2&lt;&gt;"", $L2&lt;0)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="55" priority="5">
+    <cfRule type="expression" dxfId="55" priority="6">
       <formula>$L2=""</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M2:M7">
-    <cfRule type="expression" dxfId="54" priority="6">
+    <cfRule type="expression" dxfId="54" priority="7">
       <formula>AND($M2&lt;&gt;"", $M2&gt;=0, $M2&lt;=5)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="53" priority="7">
+    <cfRule type="expression" dxfId="53" priority="8">
       <formula>AND($M2&lt;&gt;"", $M2&gt;5, $M2&lt;=30)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="52" priority="8">
+    <cfRule type="expression" dxfId="52" priority="9">
       <formula>AND($M2&lt;&gt;"", $M2&gt;30)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="51" priority="9">
+    <cfRule type="expression" dxfId="51" priority="10">
       <formula>AND($M2&lt;&gt;"", $M2&lt;0)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="50" priority="10">
+    <cfRule type="expression" dxfId="50" priority="11">
       <formula>$M2=""</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N2:N7">
-    <cfRule type="expression" dxfId="49" priority="11">
+    <cfRule type="expression" dxfId="49" priority="12">
       <formula>AND($N2&lt;&gt;"", $N2&gt;=0, $N2&lt;=5)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="48" priority="12">
+    <cfRule type="expression" dxfId="48" priority="13">
       <formula>AND($N2&lt;&gt;"", $N2&gt;5, $N2&lt;=30)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="47" priority="13">
+    <cfRule type="expression" dxfId="47" priority="14">
       <formula>AND($N2&lt;&gt;"", $N2&gt;30)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="46" priority="14">
+    <cfRule type="expression" dxfId="46" priority="15">
       <formula>AND($N2&lt;&gt;"", $N2&lt;0)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="45" priority="15">
+    <cfRule type="expression" dxfId="45" priority="16">
       <formula>$N2=""</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="O2:U7">
-    <cfRule type="expression" dxfId="44" priority="16">
+    <cfRule type="expression" dxfId="44" priority="17">
       <formula>AND($L2&lt;&gt;"", $L2&gt;=0, $L2&lt;=5)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="43" priority="17">
+    <cfRule type="expression" dxfId="43" priority="18">
       <formula>AND($L2&lt;&gt;"", $L2&gt;5, $L2&lt;=30)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="42" priority="18">
+    <cfRule type="expression" dxfId="42" priority="19">
       <formula>AND($L2&lt;&gt;"", $L2&gt;30)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="41" priority="19">
+    <cfRule type="expression" dxfId="41" priority="20">
       <formula>AND($L2&lt;&gt;"", $L2&lt;0)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="40" priority="20">
+    <cfRule type="expression" dxfId="40" priority="21">
       <formula>$L2=""</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A2:AN1000">
-    <cfRule type="expression" dxfId="95" priority="21">
+    <cfRule type="expression" dxfId="95" priority="22">
       <formula>TRIM($A2)="PAID"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="96" priority="22">
+    <cfRule type="expression" dxfId="96" priority="23">
       <formula>TRIM($A2)="Finalized"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="97" priority="23">
+    <cfRule type="expression" dxfId="97" priority="24">
       <formula>TRIM($A2)="Received"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="98" priority="24">
+    <cfRule type="expression" dxfId="98" priority="25">
       <formula>TRIM($A2)="Pending"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="99" priority="25">
+    <cfRule type="expression" dxfId="99" priority="26">
       <formula>TRIM($A2)="Under Review"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="100" priority="26">
+    <cfRule type="expression" dxfId="100" priority="27">
       <formula>AND(TRIM($A2)="Denied",$K2="")</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="103" priority="29">
+    <cfRule type="expression" dxfId="103" priority="30">
       <formula>AND(TRIM($A2)="Denied",$K2&lt;&gt;"")</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="101" priority="27">
+    <cfRule type="expression" dxfId="101" priority="28">
       <formula>TRIM($A2)="Rejected"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="102" priority="28">
+    <cfRule type="expression" dxfId="102" priority="29">
       <formula>TRIM($A2)="Not found"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -12896,14 +12971,15 @@
         <v>-95</v>
       </c>
       <c r="M2" s="12">
-        <f ca="1">IF($C2="","",$C2+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A2)="Finalized",$K2&lt;&gt;""),"",IF($C2="","",$C2+365-TODAY()))</f>
         <v>224</v>
       </c>
       <c r="N2" s="12">
-        <f ca="1">IF($C2="","",$C2+90-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A2)="Finalized",$K2&lt;&gt;""),"",IF($C2="","",$C2+90-TODAY()))</f>
         <v>-51</v>
       </c>
       <c r="O2" s="6">
+        <f>IF(AND(TRIM($A2)="Finalized",$K2&lt;&gt;""),"",DATE(2026,7,5))</f>
         <v>46208</v>
       </c>
       <c r="P2" s="5" t="s">
@@ -13100,14 +13176,15 @@
         <v>-57</v>
       </c>
       <c r="M4" s="12">
-        <f ca="1">IF($F4="","",$F4+90-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A4)="Finalized",$K4&lt;&gt;""),"",IF($F4="","",$F4+90-TODAY()))</f>
         <v>-57</v>
       </c>
       <c r="N4" s="12">
-        <f ca="1">IF($C4="","",$C4+180-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A4)="Finalized",$K4&lt;&gt;""),"",IF($C4="","",$C4+180-TODAY()))</f>
         <v>47</v>
       </c>
       <c r="O4" s="6">
+        <f>IF(AND(TRIM($A4)="Finalized",$K4&lt;&gt;""),"",DATE(2026,8,12))</f>
         <v>46246</v>
       </c>
       <c r="P4" s="5" t="s">
@@ -13211,14 +13288,15 @@
         <v>-53</v>
       </c>
       <c r="M5" s="12">
-        <f ca="1">IF($C5="","",$C5+180-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A5)="Finalized",$K5&lt;&gt;""),"",IF($C5="","",$C5+180-TODAY()))</f>
         <v>129</v>
       </c>
       <c r="N5" s="12">
-        <f ca="1">IF($C5="","",$C5+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A5)="Finalized",$K5&lt;&gt;""),"",IF($C5="","",$C5+365-TODAY()))</f>
         <v>314</v>
       </c>
       <c r="O5" s="6">
+        <f>IF(AND(TRIM($A5)="Finalized",$K5&lt;&gt;""),"",DATE(2026,8,16))</f>
         <v>46250</v>
       </c>
       <c r="P5" s="5" t="s">
@@ -13324,14 +13402,15 @@
         <v>-50</v>
       </c>
       <c r="M6" s="12">
-        <f ca="1">IF($C6="","",$C6+180-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A6)="Finalized",$K6&lt;&gt;""),"",IF($C6="","",$C6+180-TODAY()))</f>
         <v>119</v>
       </c>
       <c r="N6" s="12">
-        <f ca="1">IF($C6="","",$C6+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A6)="Finalized",$K6&lt;&gt;""),"",IF($C6="","",$C6+365-TODAY()))</f>
         <v>304</v>
       </c>
       <c r="O6" s="6">
+        <f>IF(AND(TRIM($A6)="Finalized",$K6&lt;&gt;""),"",DATE(2026,8,19))</f>
         <v>46253</v>
       </c>
       <c r="P6" s="5" t="s">
@@ -13441,14 +13520,15 @@
         <v>-44</v>
       </c>
       <c r="M7" s="12">
-        <f ca="1">IF($C7="","",$C7+180-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A7)="Finalized",$K7&lt;&gt;""),"",IF($C7="","",$C7+180-TODAY()))</f>
         <v>96</v>
       </c>
       <c r="N7" s="12">
-        <f ca="1">IF($C7="","",$C7+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A7)="Finalized",$K7&lt;&gt;""),"",IF($C7="","",$C7+365-TODAY()))</f>
         <v>281</v>
       </c>
       <c r="O7" s="6">
+        <f>IF(AND(TRIM($A7)="Finalized",$K7&lt;&gt;""),"",DATE(2026,8,25))</f>
         <v>46259</v>
       </c>
       <c r="P7" s="5" t="s">
@@ -13558,14 +13638,15 @@
         <v>-40</v>
       </c>
       <c r="M8" s="12">
-        <f ca="1">IF($C8="","",$C8+180-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A8)="Finalized",$K8&lt;&gt;""),"",IF($C8="","",$C8+180-TODAY()))</f>
         <v>66</v>
       </c>
       <c r="N8" s="12">
-        <f ca="1">IF($C8="","",$C8+180-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A8)="Finalized",$K8&lt;&gt;""),"",IF($C8="","",$C8+180-TODAY()))</f>
         <v>66</v>
       </c>
       <c r="O8" s="6">
+        <f>IF(AND(TRIM($A8)="Finalized",$K8&lt;&gt;""),"",DATE(2026,8,29))</f>
         <v>46263</v>
       </c>
       <c r="P8" s="5" t="s">
@@ -13671,14 +13752,15 @@
         <v>-27</v>
       </c>
       <c r="M9" s="12">
-        <f ca="1">IF($C9="","",$C9+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A9)="Finalized",$K9&lt;&gt;""),"",IF($C9="","",$C9+365-TODAY()))</f>
         <v>246</v>
       </c>
       <c r="N9" s="12">
-        <f ca="1">IF($C9="","",$C9+90-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A9)="Finalized",$K9&lt;&gt;""),"",IF($C9="","",$C9+90-TODAY()))</f>
         <v>-29</v>
       </c>
       <c r="O9" s="6">
+        <f>IF(AND(TRIM($A9)="Finalized",$K9&lt;&gt;""),"",DATE(2026,9,11))</f>
         <v>46276</v>
       </c>
       <c r="P9" s="5" t="s">
@@ -13784,14 +13866,15 @@
         <v>205</v>
       </c>
       <c r="M10" s="12">
-        <f ca="1">IF($C10="","",$C10+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A10)="Finalized",$K10&lt;&gt;""),"",IF($C10="","",$C10+365-TODAY()))</f>
         <v>219</v>
       </c>
       <c r="N10" s="12">
-        <f ca="1">IF($C10="","",$C10+120-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A10)="Finalized",$K10&lt;&gt;""),"",IF($C10="","",$C10+120-TODAY()))</f>
         <v>-26</v>
       </c>
       <c r="O10" s="6">
+        <f>IF(AND(TRIM($A10)="Finalized",$K10&lt;&gt;""),"",DATE(2027,5,1))</f>
         <v>46508</v>
       </c>
       <c r="P10" s="5" t="s">
@@ -13897,14 +13980,15 @@
         <v>208</v>
       </c>
       <c r="M11" s="12">
-        <f ca="1">IF($C11="","",$C11+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A11)="Finalized",$K11&lt;&gt;""),"",IF($C11="","",$C11+365-TODAY()))</f>
         <v>223</v>
       </c>
       <c r="N11" s="12">
-        <f ca="1">IF($C11="","",$C11+120-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A11)="Finalized",$K11&lt;&gt;""),"",IF($C11="","",$C11+120-TODAY()))</f>
         <v>-22</v>
       </c>
       <c r="O11" s="6">
+        <f>IF(AND(TRIM($A11)="Finalized",$K11&lt;&gt;""),"",DATE(2027,5,4))</f>
         <v>46511</v>
       </c>
       <c r="P11" s="5" t="s">
@@ -14014,14 +14098,15 @@
         <v>215</v>
       </c>
       <c r="M12" s="12">
-        <f ca="1">IF($C12="","",$C12+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A12)="Finalized",$K12&lt;&gt;""),"",IF($C12="","",$C12+365-TODAY()))</f>
         <v>307</v>
       </c>
       <c r="N12" s="12">
-        <f ca="1">IF($C12="","",$C12+120-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A12)="Finalized",$K12&lt;&gt;""),"",IF($C12="","",$C12+120-TODAY()))</f>
         <v>62</v>
       </c>
       <c r="O12" s="6">
+        <f>IF(AND(TRIM($A12)="Finalized",$K12&lt;&gt;""),"",DATE(2027,5,11))</f>
         <v>46518</v>
       </c>
       <c r="P12" s="5" t="s">
@@ -14125,14 +14210,15 @@
         <v>217</v>
       </c>
       <c r="M13" s="12">
-        <f ca="1">IF($C13="","",$C13+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A13)="Finalized",$K13&lt;&gt;""),"",IF($C13="","",$C13+365-TODAY()))</f>
         <v>230</v>
       </c>
       <c r="N13" s="12">
-        <f ca="1">IF($C13="","",$C13+120-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A13)="Finalized",$K13&lt;&gt;""),"",IF($C13="","",$C13+120-TODAY()))</f>
         <v>-15</v>
       </c>
       <c r="O13" s="6">
+        <f>IF(AND(TRIM($A13)="Finalized",$K13&lt;&gt;""),"",DATE(2027,5,13))</f>
         <v>46520</v>
       </c>
       <c r="P13" s="5" t="s">
@@ -14238,14 +14324,15 @@
         <v>219</v>
       </c>
       <c r="M14" s="12">
-        <f ca="1">IF($C14="","",$C14+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A14)="Finalized",$K14&lt;&gt;""),"",IF($C14="","",$C14+365-TODAY()))</f>
         <v>230</v>
       </c>
       <c r="N14" s="12">
-        <f ca="1">IF($C14="","",$C14+120-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A14)="Finalized",$K14&lt;&gt;""),"",IF($C14="","",$C14+120-TODAY()))</f>
         <v>-15</v>
       </c>
       <c r="O14" s="6">
+        <f>IF(AND(TRIM($A14)="Finalized",$K14&lt;&gt;""),"",DATE(2027,5,15))</f>
         <v>46522</v>
       </c>
       <c r="P14" s="5" t="s">
@@ -14353,14 +14440,15 @@
         <v>233</v>
       </c>
       <c r="M15" s="12">
-        <f ca="1">IF($C15="","",$C15+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A15)="Finalized",$K15&lt;&gt;""),"",IF($C15="","",$C15+365-TODAY()))</f>
         <v>251</v>
       </c>
       <c r="N15" s="12">
-        <f ca="1">IF($C15="","",$C15+120-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A15)="Finalized",$K15&lt;&gt;""),"",IF($C15="","",$C15+120-TODAY()))</f>
         <v>6</v>
       </c>
       <c r="O15" s="6">
+        <f>IF(AND(TRIM($A15)="Finalized",$K15&lt;&gt;""),"",DATE(2027,5,29))</f>
         <v>46536</v>
       </c>
       <c r="P15" s="5" t="s">
@@ -14468,14 +14556,15 @@
         <v>-67</v>
       </c>
       <c r="M16" s="12">
-        <f ca="1">IF($C16="","",$C16+180-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A16)="Finalized",$K16&lt;&gt;""),"",IF($C16="","",$C16+180-TODAY()))</f>
         <v>47</v>
       </c>
       <c r="N16" s="12">
-        <f ca="1">IF($C16="","",$C16+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A16)="Finalized",$K16&lt;&gt;""),"",IF($C16="","",$C16+365-TODAY()))</f>
         <v>232</v>
       </c>
       <c r="O16" s="6">
+        <f>IF(AND(TRIM($A16)="Finalized",$K16&lt;&gt;""),"",DATE(2026,8,2))</f>
         <v>46236</v>
       </c>
       <c r="P16" s="5" t="s">
@@ -14579,14 +14668,15 @@
         <v>-65</v>
       </c>
       <c r="M17" s="12">
-        <f ca="1">IF($F17="","",$F17+90-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A17)="Finalized",$K17&lt;&gt;""),"",IF($F17="","",$F17+90-TODAY()))</f>
         <v>-65</v>
       </c>
       <c r="N17" s="12">
-        <f ca="1">IF($C17="","",$C17+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A17)="Finalized",$K17&lt;&gt;""),"",IF($C17="","",$C17+365-TODAY()))</f>
         <v>259</v>
       </c>
       <c r="O17" s="6">
+        <f>IF(AND(TRIM($A17)="Finalized",$K17&lt;&gt;""),"",DATE(2026,8,4))</f>
         <v>46238</v>
       </c>
       <c r="P17" s="5" t="s">
@@ -14692,14 +14782,15 @@
         <v>-58</v>
       </c>
       <c r="M18" s="12">
-        <f ca="1">IF($C18="","",$C18+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A18)="Finalized",$K18&lt;&gt;""),"",IF($C18="","",$C18+365-TODAY()))</f>
         <v>324</v>
       </c>
       <c r="N18" s="12">
-        <f ca="1">IF($C18="","",$C18+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A18)="Finalized",$K18&lt;&gt;""),"",IF($C18="","",$C18+365-TODAY()))</f>
         <v>324</v>
       </c>
       <c r="O18" s="6">
+        <f>IF(AND(TRIM($A18)="Finalized",$K18&lt;&gt;""),"",DATE(2026,8,11))</f>
         <v>46245</v>
       </c>
       <c r="P18" s="5" t="s">
@@ -14804,20 +14895,21 @@
       <c r="K19" s="3">
         <v>46245</v>
       </c>
-      <c r="L19" s="12">
+      <c t="str" r="L19" s="12">
         <f ca="1">IF($O19="","",$O19-TODAY())</f>
-        <v>-51</v>
-      </c>
-      <c r="M19" s="12">
-        <f ca="1">IF($C19="","",$C19+90-TODAY())</f>
-        <v>-43</v>
-      </c>
-      <c r="N19" s="12">
-        <f ca="1">IF($C19="","",$C19+90-TODAY())</f>
-        <v>-43</v>
-      </c>
-      <c r="O19" s="6">
-        <v>46252</v>
+        <v/>
+      </c>
+      <c t="str" r="M19" s="12">
+        <f ca="1">IF(AND(TRIM($A19)="Finalized",$K19&lt;&gt;""),"",IF($C19="","",$C19+90-TODAY()))</f>
+        <v/>
+      </c>
+      <c t="str" r="N19" s="12">
+        <f ca="1">IF(AND(TRIM($A19)="Finalized",$K19&lt;&gt;""),"",IF($C19="","",$C19+90-TODAY()))</f>
+        <v/>
+      </c>
+      <c t="str" r="O19" s="6">
+        <f>IF(AND(TRIM($A19)="Finalized",$K19&lt;&gt;""),"",DATE(2026,8,18))</f>
+        <v/>
       </c>
       <c r="P19" s="5" t="s">
         <v>65</v>
@@ -14919,20 +15011,21 @@
       <c r="K20" s="3">
         <v>46245</v>
       </c>
-      <c r="L20" s="12">
+      <c t="str" r="L20" s="12">
         <f ca="1">IF($O20="","",$O20-TODAY())</f>
-        <v>-45</v>
-      </c>
-      <c r="M20" s="12">
-        <f ca="1">IF($F20="","",$F20+90-TODAY())</f>
-        <v>-45</v>
-      </c>
-      <c r="N20" s="12">
-        <f ca="1">IF($C20="","",$C20+180-TODAY())</f>
-        <v>108</v>
-      </c>
-      <c r="O20" s="6">
-        <v>46258</v>
+        <v/>
+      </c>
+      <c t="str" r="M20" s="12">
+        <f ca="1">IF(AND(TRIM($A20)="Finalized",$K20&lt;&gt;""),"",IF($F20="","",$F20+90-TODAY()))</f>
+        <v/>
+      </c>
+      <c t="str" r="N20" s="12">
+        <f ca="1">IF(AND(TRIM($A20)="Finalized",$K20&lt;&gt;""),"",IF($C20="","",$C20+180-TODAY()))</f>
+        <v/>
+      </c>
+      <c t="str" r="O20" s="6">
+        <f>IF(AND(TRIM($A20)="Finalized",$K20&lt;&gt;""),"",DATE(2026,8,24))</f>
+        <v/>
       </c>
       <c r="P20" s="5" t="s">
         <v>46</v>
@@ -15030,20 +15123,21 @@
       <c r="K21" s="3">
         <v>46250</v>
       </c>
-      <c r="L21" s="12">
+      <c t="str" r="L21" s="12">
         <f ca="1">IF($O21="","",$O21-TODAY())</f>
-        <v>-30</v>
-      </c>
-      <c r="M21" s="12">
-        <f ca="1">IF($C21="","",$C21+180-TODAY())</f>
-        <v>41</v>
-      </c>
-      <c r="N21" s="12">
-        <f ca="1">IF($C21="","",$C21+180-TODAY())</f>
-        <v>41</v>
-      </c>
-      <c r="O21" s="6">
-        <v>46273</v>
+        <v/>
+      </c>
+      <c t="str" r="M21" s="12">
+        <f ca="1">IF(AND(TRIM($A21)="Finalized",$K21&lt;&gt;""),"",IF($C21="","",$C21+180-TODAY()))</f>
+        <v/>
+      </c>
+      <c t="str" r="N21" s="12">
+        <f ca="1">IF(AND(TRIM($A21)="Finalized",$K21&lt;&gt;""),"",IF($C21="","",$C21+180-TODAY()))</f>
+        <v/>
+      </c>
+      <c t="str" r="O21" s="6">
+        <f>IF(AND(TRIM($A21)="Finalized",$K21&lt;&gt;""),"",DATE(2026,9,8))</f>
+        <v/>
       </c>
       <c r="P21" s="5" t="s">
         <v>103</v>
@@ -15149,20 +15243,21 @@
       <c r="K22" s="3">
         <v>46250</v>
       </c>
-      <c r="L22" s="12">
+      <c t="str" r="L22" s="12">
         <f ca="1">IF($O22="","",$O22-TODAY())</f>
-        <v>-27</v>
-      </c>
-      <c r="M22" s="12">
-        <f ca="1">IF($C22="","",$C22+180-TODAY())</f>
-        <v>48</v>
-      </c>
-      <c r="N22" s="12">
-        <f ca="1">IF($C22="","",$C22+180-TODAY())</f>
-        <v>48</v>
-      </c>
-      <c r="O22" s="6">
-        <v>46276</v>
+        <v/>
+      </c>
+      <c t="str" r="M22" s="12">
+        <f ca="1">IF(AND(TRIM($A22)="Finalized",$K22&lt;&gt;""),"",IF($C22="","",$C22+180-TODAY()))</f>
+        <v/>
+      </c>
+      <c t="str" r="N22" s="12">
+        <f ca="1">IF(AND(TRIM($A22)="Finalized",$K22&lt;&gt;""),"",IF($C22="","",$C22+180-TODAY()))</f>
+        <v/>
+      </c>
+      <c t="str" r="O22" s="6">
+        <f>IF(AND(TRIM($A22)="Finalized",$K22&lt;&gt;""),"",DATE(2026,9,11))</f>
+        <v/>
       </c>
       <c r="P22" s="5" t="s">
         <v>103</v>
@@ -15260,20 +15355,21 @@
       <c r="K23" s="3">
         <v>46252</v>
       </c>
-      <c r="L23" s="12">
+      <c t="str" r="L23" s="12">
         <f ca="1">IF($O23="","",$O23-TODAY())</f>
-        <v>33</v>
-      </c>
-      <c r="M23" s="12">
-        <f ca="1">IF($F23="","",$F23+180-TODAY())</f>
-        <v>33</v>
-      </c>
-      <c r="N23" s="12">
-        <f ca="1">IF($C23="","",$C23+180-TODAY())</f>
-        <v>47</v>
-      </c>
-      <c r="O23" s="6">
-        <v>46336</v>
+        <v/>
+      </c>
+      <c t="str" r="M23" s="12">
+        <f ca="1">IF(AND(TRIM($A23)="Finalized",$K23&lt;&gt;""),"",IF($F23="","",$F23+180-TODAY()))</f>
+        <v/>
+      </c>
+      <c t="str" r="N23" s="12">
+        <f ca="1">IF(AND(TRIM($A23)="Finalized",$K23&lt;&gt;""),"",IF($C23="","",$C23+180-TODAY()))</f>
+        <v/>
+      </c>
+      <c t="str" r="O23" s="6">
+        <f>IF(AND(TRIM($A23)="Finalized",$K23&lt;&gt;""),"",DATE(2026,11,10))</f>
+        <v/>
       </c>
       <c r="P23" s="5" t="s">
         <v>48</v>
@@ -15339,100 +15435,105 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:AN23" xr:uid="{00000000-0009-0000-0000-000003000000}"/>
+  <conditionalFormatting sqref="L2:O1000">
+    <cfRule type="expression" dxfId="96" priority="1" stopIfTrue="1">
+      <formula>AND(TRIM($A2)="Finalized",$K2&lt;&gt;"")</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="L2:L23">
-    <cfRule type="expression" dxfId="39" priority="1">
+    <cfRule type="expression" dxfId="39" priority="2">
       <formula>AND($L2&lt;&gt;"", $L2&gt;=0, $L2&lt;=5)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="38" priority="2">
+    <cfRule type="expression" dxfId="38" priority="3">
       <formula>AND($L2&lt;&gt;"", $L2&gt;5, $L2&lt;=30)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="37" priority="3">
+    <cfRule type="expression" dxfId="37" priority="4">
       <formula>AND($L2&lt;&gt;"", $L2&gt;30)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="36" priority="4">
+    <cfRule type="expression" dxfId="36" priority="5">
       <formula>AND($L2&lt;&gt;"", $L2&lt;0)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="35" priority="5">
+    <cfRule type="expression" dxfId="35" priority="6">
       <formula>$L2=""</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M2:M23">
-    <cfRule type="expression" dxfId="34" priority="6">
+    <cfRule type="expression" dxfId="34" priority="7">
       <formula>AND($M2&lt;&gt;"", $M2&gt;=0, $M2&lt;=5)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="33" priority="7">
+    <cfRule type="expression" dxfId="33" priority="8">
       <formula>AND($M2&lt;&gt;"", $M2&gt;5, $M2&lt;=30)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="32" priority="8">
+    <cfRule type="expression" dxfId="32" priority="9">
       <formula>AND($M2&lt;&gt;"", $M2&gt;30)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="31" priority="9">
+    <cfRule type="expression" dxfId="31" priority="10">
       <formula>AND($M2&lt;&gt;"", $M2&lt;0)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="30" priority="10">
+    <cfRule type="expression" dxfId="30" priority="11">
       <formula>$M2=""</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N2:N23">
-    <cfRule type="expression" dxfId="29" priority="11">
+    <cfRule type="expression" dxfId="29" priority="12">
       <formula>AND($N2&lt;&gt;"", $N2&gt;=0, $N2&lt;=5)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="28" priority="12">
+    <cfRule type="expression" dxfId="28" priority="13">
       <formula>AND($N2&lt;&gt;"", $N2&gt;5, $N2&lt;=30)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="27" priority="13">
+    <cfRule type="expression" dxfId="27" priority="14">
       <formula>AND($N2&lt;&gt;"", $N2&gt;30)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="26" priority="14">
+    <cfRule type="expression" dxfId="26" priority="15">
       <formula>AND($N2&lt;&gt;"", $N2&lt;0)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="25" priority="15">
+    <cfRule type="expression" dxfId="25" priority="16">
       <formula>$N2=""</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="O2:U23">
-    <cfRule type="expression" dxfId="24" priority="16">
+    <cfRule type="expression" dxfId="24" priority="17">
       <formula>AND($L2&lt;&gt;"", $L2&gt;=0, $L2&lt;=5)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="23" priority="17">
+    <cfRule type="expression" dxfId="23" priority="18">
       <formula>AND($L2&lt;&gt;"", $L2&gt;5, $L2&lt;=30)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="22" priority="18">
+    <cfRule type="expression" dxfId="22" priority="19">
       <formula>AND($L2&lt;&gt;"", $L2&gt;30)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="21" priority="19">
+    <cfRule type="expression" dxfId="21" priority="20">
       <formula>AND($L2&lt;&gt;"", $L2&lt;0)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="20" priority="20">
+    <cfRule type="expression" dxfId="20" priority="21">
       <formula>$L2=""</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A2:AN1000">
-    <cfRule type="expression" dxfId="95" priority="21">
+    <cfRule type="expression" dxfId="95" priority="22">
       <formula>TRIM($A2)="PAID"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="96" priority="22">
+    <cfRule type="expression" dxfId="96" priority="23">
       <formula>TRIM($A2)="Finalized"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="97" priority="23">
+    <cfRule type="expression" dxfId="97" priority="24">
       <formula>TRIM($A2)="Received"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="98" priority="24">
+    <cfRule type="expression" dxfId="98" priority="25">
       <formula>TRIM($A2)="Pending"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="99" priority="25">
+    <cfRule type="expression" dxfId="99" priority="26">
       <formula>TRIM($A2)="Under Review"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="100" priority="26">
+    <cfRule type="expression" dxfId="100" priority="27">
       <formula>AND(TRIM($A2)="Denied",$K2="")</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="103" priority="29">
+    <cfRule type="expression" dxfId="103" priority="30">
       <formula>AND(TRIM($A2)="Denied",$K2&lt;&gt;"")</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="101" priority="27">
+    <cfRule type="expression" dxfId="101" priority="28">
       <formula>TRIM($A2)="Rejected"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="102" priority="28">
+    <cfRule type="expression" dxfId="102" priority="29">
       <formula>TRIM($A2)="Not found"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -15649,14 +15750,15 @@
         <v>-50</v>
       </c>
       <c r="M2" s="12">
-        <f ca="1">IF($C2="","",$C2+180-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A2)="Finalized",$K2&lt;&gt;""),"",IF($C2="","",$C2+180-TODAY()))</f>
         <v>136</v>
       </c>
       <c r="N2" s="12">
-        <f ca="1">IF($C2="","",$C2+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A2)="Finalized",$K2&lt;&gt;""),"",IF($C2="","",$C2+365-TODAY()))</f>
         <v>321</v>
       </c>
       <c r="O2" s="6">
+        <f>IF(AND(TRIM($A2)="Finalized",$K2&lt;&gt;""),"",DATE(2026,8,19))</f>
         <v>46253</v>
       </c>
       <c r="P2" s="5" t="s">
@@ -15758,14 +15860,15 @@
         <v>-45</v>
       </c>
       <c r="M3" s="12">
-        <f ca="1">IF($F3="","",$F3+90-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A3)="Finalized",$K3&lt;&gt;""),"",IF($F3="","",$F3+90-TODAY()))</f>
         <v>-45</v>
       </c>
       <c r="N3" s="12">
-        <f ca="1">IF($C3="","",$C3+180-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A3)="Finalized",$K3&lt;&gt;""),"",IF($C3="","",$C3+180-TODAY()))</f>
         <v>58</v>
       </c>
       <c r="O3" s="6">
+        <f>IF(AND(TRIM($A3)="Finalized",$K3&lt;&gt;""),"",DATE(2026,8,24))</f>
         <v>46258</v>
       </c>
       <c r="P3" s="5" t="s">
@@ -15873,14 +15976,15 @@
         <v>-44</v>
       </c>
       <c r="M4" s="12">
-        <f ca="1">IF($F4="","",$F4+90-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A4)="Finalized",$K4&lt;&gt;""),"",IF($F4="","",$F4+90-TODAY()))</f>
         <v>-44</v>
       </c>
       <c r="N4" s="12">
-        <f ca="1">IF($C4="","",$C4+180-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A4)="Finalized",$K4&lt;&gt;""),"",IF($C4="","",$C4+180-TODAY()))</f>
         <v>54</v>
       </c>
       <c r="O4" s="6">
+        <f>IF(AND(TRIM($A4)="Finalized",$K4&lt;&gt;""),"",DATE(2026,8,25))</f>
         <v>46259</v>
       </c>
       <c r="P4" s="5" t="s">
@@ -15990,14 +16094,15 @@
         <v>-34</v>
       </c>
       <c r="M5" s="12">
-        <f ca="1">IF($C5="","",$C5+180-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A5)="Finalized",$K5&lt;&gt;""),"",IF($C5="","",$C5+180-TODAY()))</f>
         <v>59</v>
       </c>
       <c r="N5" s="12">
-        <f ca="1">IF($C5="","",$C5+180-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A5)="Finalized",$K5&lt;&gt;""),"",IF($C5="","",$C5+180-TODAY()))</f>
         <v>59</v>
       </c>
       <c r="O5" s="6">
+        <f>IF(AND(TRIM($A5)="Finalized",$K5&lt;&gt;""),"",DATE(2026,9,4))</f>
         <v>46269</v>
       </c>
       <c r="P5" s="5" t="s">
@@ -16103,14 +16208,15 @@
         <v>209</v>
       </c>
       <c r="M6" s="12">
-        <f ca="1">IF($C6="","",$C6+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A6)="Finalized",$K6&lt;&gt;""),"",IF($C6="","",$C6+365-TODAY()))</f>
         <v>233</v>
       </c>
       <c r="N6" s="12">
-        <f ca="1">IF($C6="","",$C6+120-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A6)="Finalized",$K6&lt;&gt;""),"",IF($C6="","",$C6+120-TODAY()))</f>
         <v>-12</v>
       </c>
       <c r="O6" s="6">
+        <f>IF(AND(TRIM($A6)="Finalized",$K6&lt;&gt;""),"",DATE(2027,5,5))</f>
         <v>46512</v>
       </c>
       <c r="P6" s="5" t="s">
@@ -16218,14 +16324,15 @@
         <v>216</v>
       </c>
       <c r="M7" s="12">
-        <f ca="1">IF($C7="","",$C7+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A7)="Finalized",$K7&lt;&gt;""),"",IF($C7="","",$C7+365-TODAY()))</f>
         <v>265</v>
       </c>
       <c r="N7" s="12">
-        <f ca="1">IF($C7="","",$C7+120-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A7)="Finalized",$K7&lt;&gt;""),"",IF($C7="","",$C7+120-TODAY()))</f>
         <v>20</v>
       </c>
       <c r="O7" s="6">
+        <f>IF(AND(TRIM($A7)="Finalized",$K7&lt;&gt;""),"",DATE(2027,5,12))</f>
         <v>46519</v>
       </c>
       <c r="P7" s="5" t="s">
@@ -16329,14 +16436,15 @@
         <v>223</v>
       </c>
       <c r="M8" s="12">
-        <f ca="1">IF($C8="","",$C8+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A8)="Finalized",$K8&lt;&gt;""),"",IF($C8="","",$C8+365-TODAY()))</f>
         <v>240</v>
       </c>
       <c r="N8" s="12">
-        <f ca="1">IF($C8="","",$C8+120-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A8)="Finalized",$K8&lt;&gt;""),"",IF($C8="","",$C8+120-TODAY()))</f>
         <v>-5</v>
       </c>
       <c r="O8" s="6">
+        <f>IF(AND(TRIM($A8)="Finalized",$K8&lt;&gt;""),"",DATE(2027,5,19))</f>
         <v>46526</v>
       </c>
       <c r="P8" s="5" t="s">
@@ -16444,14 +16552,15 @@
         <v>224</v>
       </c>
       <c r="M9" s="12">
-        <f ca="1">IF($C9="","",$C9+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A9)="Finalized",$K9&lt;&gt;""),"",IF($C9="","",$C9+365-TODAY()))</f>
         <v>240</v>
       </c>
       <c r="N9" s="12">
-        <f ca="1">IF($C9="","",$C9+120-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A9)="Finalized",$K9&lt;&gt;""),"",IF($C9="","",$C9+120-TODAY()))</f>
         <v>-5</v>
       </c>
       <c r="O9" s="6">
+        <f>IF(AND(TRIM($A9)="Finalized",$K9&lt;&gt;""),"",DATE(2027,5,20))</f>
         <v>46527</v>
       </c>
       <c r="P9" s="5" t="s">
@@ -16555,14 +16664,15 @@
         <v>-58</v>
       </c>
       <c r="M10" s="12">
-        <f ca="1">IF($C10="","",$C10+180-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A10)="Finalized",$K10&lt;&gt;""),"",IF($C10="","",$C10+180-TODAY()))</f>
         <v>47</v>
       </c>
       <c r="N10" s="12">
-        <f ca="1">IF($C10="","",$C10+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A10)="Finalized",$K10&lt;&gt;""),"",IF($C10="","",$C10+365-TODAY()))</f>
         <v>232</v>
       </c>
       <c r="O10" s="6">
+        <f>IF(AND(TRIM($A10)="Finalized",$K10&lt;&gt;""),"",DATE(2026,8,11))</f>
         <v>46245</v>
       </c>
       <c r="P10" s="5" t="s">
@@ -16670,14 +16780,15 @@
         <v>-64</v>
       </c>
       <c r="M11" s="12">
-        <f ca="1">IF($C11="","",$C11+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A11)="Finalized",$K11&lt;&gt;""),"",IF($C11="","",$C11+365-TODAY()))</f>
         <v>298</v>
       </c>
       <c r="N11" s="12">
-        <f ca="1">IF($C11="","",$C11+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A11)="Finalized",$K11&lt;&gt;""),"",IF($C11="","",$C11+365-TODAY()))</f>
         <v>298</v>
       </c>
       <c r="O11" s="6">
+        <f>IF(AND(TRIM($A11)="Finalized",$K11&lt;&gt;""),"",DATE(2026,8,5))</f>
         <v>46239</v>
       </c>
       <c r="P11" s="5" t="s">
@@ -16780,20 +16891,21 @@
       <c r="K12" s="3">
         <v>46246</v>
       </c>
-      <c r="L12" s="12">
+      <c t="str" r="L12" s="12">
         <f ca="1">IF($O12="","",$O12-TODAY())</f>
-        <v>-50</v>
-      </c>
-      <c r="M12" s="12">
-        <f ca="1">IF($F12="","",$F12+90-TODAY())</f>
-        <v>-50</v>
-      </c>
-      <c r="N12" s="12">
-        <f ca="1">IF($C12="","",$C12+180-TODAY())</f>
-        <v>59</v>
-      </c>
-      <c r="O12" s="6">
-        <v>46253</v>
+        <v/>
+      </c>
+      <c t="str" r="M12" s="12">
+        <f ca="1">IF(AND(TRIM($A12)="Finalized",$K12&lt;&gt;""),"",IF($F12="","",$F12+90-TODAY()))</f>
+        <v/>
+      </c>
+      <c t="str" r="N12" s="12">
+        <f ca="1">IF(AND(TRIM($A12)="Finalized",$K12&lt;&gt;""),"",IF($C12="","",$C12+180-TODAY()))</f>
+        <v/>
+      </c>
+      <c t="str" r="O12" s="6">
+        <f>IF(AND(TRIM($A12)="Finalized",$K12&lt;&gt;""),"",DATE(2026,8,19))</f>
+        <v/>
       </c>
       <c r="P12" s="5" t="s">
         <v>46</v>
@@ -16891,20 +17003,21 @@
       <c r="K13" s="3">
         <v>46251</v>
       </c>
-      <c r="L13" s="12">
+      <c t="str" r="L13" s="12">
         <f ca="1">IF($O13="","",$O13-TODAY())</f>
-        <v>-45</v>
-      </c>
-      <c r="M13" s="12">
-        <f ca="1">IF($F13="","",$F13+90-TODAY())</f>
-        <v>-45</v>
-      </c>
-      <c r="N13" s="12">
-        <f ca="1">IF($C13="","",$C13+60-TODAY())</f>
-        <v>-68</v>
-      </c>
-      <c r="O13" s="6">
-        <v>46258</v>
+        <v/>
+      </c>
+      <c t="str" r="M13" s="12">
+        <f ca="1">IF(AND(TRIM($A13)="Finalized",$K13&lt;&gt;""),"",IF($F13="","",$F13+90-TODAY()))</f>
+        <v/>
+      </c>
+      <c t="str" r="N13" s="12">
+        <f ca="1">IF(AND(TRIM($A13)="Finalized",$K13&lt;&gt;""),"",IF($C13="","",$C13+60-TODAY()))</f>
+        <v/>
+      </c>
+      <c t="str" r="O13" s="6">
+        <f>IF(AND(TRIM($A13)="Finalized",$K13&lt;&gt;""),"",DATE(2026,8,24))</f>
+        <v/>
       </c>
       <c r="P13" s="5" t="s">
         <v>46</v>
@@ -17004,20 +17117,21 @@
       <c r="K14" s="3">
         <v>46252</v>
       </c>
-      <c r="L14" s="12">
+      <c t="str" r="L14" s="12">
         <f ca="1">IF($O14="","",$O14-TODAY())</f>
-        <v>-36</v>
-      </c>
-      <c r="M14" s="12">
-        <f ca="1">IF($C14="","",$C14+180-TODAY())</f>
-        <v>62</v>
-      </c>
-      <c r="N14" s="12">
-        <f ca="1">IF($C14="","",$C14+180-TODAY())</f>
-        <v>62</v>
-      </c>
-      <c r="O14" s="6">
-        <v>46267</v>
+        <v/>
+      </c>
+      <c t="str" r="M14" s="12">
+        <f ca="1">IF(AND(TRIM($A14)="Finalized",$K14&lt;&gt;""),"",IF($C14="","",$C14+180-TODAY()))</f>
+        <v/>
+      </c>
+      <c t="str" r="N14" s="12">
+        <f ca="1">IF(AND(TRIM($A14)="Finalized",$K14&lt;&gt;""),"",IF($C14="","",$C14+180-TODAY()))</f>
+        <v/>
+      </c>
+      <c t="str" r="O14" s="6">
+        <f>IF(AND(TRIM($A14)="Finalized",$K14&lt;&gt;""),"",DATE(2026,9,2))</f>
+        <v/>
       </c>
       <c r="P14" s="5" t="s">
         <v>103</v>
@@ -17115,20 +17229,21 @@
       <c r="K15" s="3">
         <v>46258</v>
       </c>
-      <c r="L15" s="12">
+      <c t="str" r="L15" s="12">
         <f ca="1">IF($O15="","",$O15-TODAY())</f>
-        <v>217</v>
-      </c>
-      <c r="M15" s="12">
-        <f ca="1">IF($C15="","",$C15+365-TODAY())</f>
-        <v>307</v>
-      </c>
-      <c r="N15" s="12">
-        <f ca="1">IF($C15="","",$C15+120-TODAY())</f>
-        <v>62</v>
-      </c>
-      <c r="O15" s="6">
-        <v>46520</v>
+        <v/>
+      </c>
+      <c t="str" r="M15" s="12">
+        <f ca="1">IF(AND(TRIM($A15)="Finalized",$K15&lt;&gt;""),"",IF($C15="","",$C15+365-TODAY()))</f>
+        <v/>
+      </c>
+      <c t="str" r="N15" s="12">
+        <f ca="1">IF(AND(TRIM($A15)="Finalized",$K15&lt;&gt;""),"",IF($C15="","",$C15+120-TODAY()))</f>
+        <v/>
+      </c>
+      <c t="str" r="O15" s="6">
+        <f>IF(AND(TRIM($A15)="Finalized",$K15&lt;&gt;""),"",DATE(2027,5,13))</f>
+        <v/>
       </c>
       <c r="P15" s="5" t="s">
         <v>50</v>
@@ -17233,14 +17348,15 @@
         <v>-59</v>
       </c>
       <c r="M16" s="12">
-        <f ca="1">IF($F16="","",$F16+90-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A16)="Finalized",$K16&lt;&gt;""),"",IF($F16="","",$F16+90-TODAY()))</f>
         <v>-59</v>
       </c>
       <c r="N16" s="12">
-        <f ca="1">IF($C16="","",$C16+180-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A16)="Finalized",$K16&lt;&gt;""),"",IF($C16="","",$C16+180-TODAY()))</f>
         <v>125</v>
       </c>
       <c r="O16" s="6">
+        <f>IF(AND(TRIM($A16)="Finalized",$K16&lt;&gt;""),"",DATE(2026,8,10))</f>
         <v>46244</v>
       </c>
       <c r="P16" s="5" t="s">
@@ -17309,100 +17425,105 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:AN16" xr:uid="{00000000-0009-0000-0000-000004000000}"/>
+  <conditionalFormatting sqref="L2:O1000">
+    <cfRule type="expression" dxfId="96" priority="1" stopIfTrue="1">
+      <formula>AND(TRIM($A2)="Finalized",$K2&lt;&gt;"")</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="L2:L16">
-    <cfRule type="expression" dxfId="19" priority="1">
+    <cfRule type="expression" dxfId="19" priority="2">
       <formula>AND($L2&lt;&gt;"", $L2&gt;=0, $L2&lt;=5)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="18" priority="2">
+    <cfRule type="expression" dxfId="18" priority="3">
       <formula>AND($L2&lt;&gt;"", $L2&gt;5, $L2&lt;=30)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="17" priority="3">
+    <cfRule type="expression" dxfId="17" priority="4">
       <formula>AND($L2&lt;&gt;"", $L2&gt;30)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="16" priority="4">
+    <cfRule type="expression" dxfId="16" priority="5">
       <formula>AND($L2&lt;&gt;"", $L2&lt;0)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="15" priority="5">
+    <cfRule type="expression" dxfId="15" priority="6">
       <formula>$L2=""</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M2:M16">
-    <cfRule type="expression" dxfId="14" priority="6">
+    <cfRule type="expression" dxfId="14" priority="7">
       <formula>AND($M2&lt;&gt;"", $M2&gt;=0, $M2&lt;=5)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="13" priority="7">
+    <cfRule type="expression" dxfId="13" priority="8">
       <formula>AND($M2&lt;&gt;"", $M2&gt;5, $M2&lt;=30)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="12" priority="8">
+    <cfRule type="expression" dxfId="12" priority="9">
       <formula>AND($M2&lt;&gt;"", $M2&gt;30)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="11" priority="9">
+    <cfRule type="expression" dxfId="11" priority="10">
       <formula>AND($M2&lt;&gt;"", $M2&lt;0)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="10" priority="10">
+    <cfRule type="expression" dxfId="10" priority="11">
       <formula>$M2=""</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N2:N16">
-    <cfRule type="expression" dxfId="9" priority="11">
+    <cfRule type="expression" dxfId="9" priority="12">
       <formula>AND($N2&lt;&gt;"", $N2&gt;=0, $N2&lt;=5)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="8" priority="12">
+    <cfRule type="expression" dxfId="8" priority="13">
       <formula>AND($N2&lt;&gt;"", $N2&gt;5, $N2&lt;=30)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="7" priority="13">
+    <cfRule type="expression" dxfId="7" priority="14">
       <formula>AND($N2&lt;&gt;"", $N2&gt;30)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="6" priority="14">
+    <cfRule type="expression" dxfId="6" priority="15">
       <formula>AND($N2&lt;&gt;"", $N2&lt;0)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="5" priority="15">
+    <cfRule type="expression" dxfId="5" priority="16">
       <formula>$N2=""</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="O2:U16">
-    <cfRule type="expression" dxfId="4" priority="16">
+    <cfRule type="expression" dxfId="4" priority="17">
       <formula>AND($L2&lt;&gt;"", $L2&gt;=0, $L2&lt;=5)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="3" priority="17">
+    <cfRule type="expression" dxfId="3" priority="18">
       <formula>AND($L2&lt;&gt;"", $L2&gt;5, $L2&lt;=30)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="2" priority="18">
+    <cfRule type="expression" dxfId="2" priority="19">
       <formula>AND($L2&lt;&gt;"", $L2&gt;30)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="1" priority="19">
+    <cfRule type="expression" dxfId="1" priority="20">
       <formula>AND($L2&lt;&gt;"", $L2&lt;0)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="0" priority="20">
+    <cfRule type="expression" dxfId="0" priority="21">
       <formula>$L2=""</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A2:AN1000">
-    <cfRule type="expression" dxfId="95" priority="21">
+    <cfRule type="expression" dxfId="95" priority="22">
       <formula>TRIM($A2)="PAID"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="96" priority="22">
+    <cfRule type="expression" dxfId="96" priority="23">
       <formula>TRIM($A2)="Finalized"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="97" priority="23">
+    <cfRule type="expression" dxfId="97" priority="24">
       <formula>TRIM($A2)="Received"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="98" priority="24">
+    <cfRule type="expression" dxfId="98" priority="25">
       <formula>TRIM($A2)="Pending"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="99" priority="25">
+    <cfRule type="expression" dxfId="99" priority="26">
       <formula>TRIM($A2)="Under Review"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="100" priority="26">
+    <cfRule type="expression" dxfId="100" priority="27">
       <formula>AND(TRIM($A2)="Denied",$K2="")</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="103" priority="29">
+    <cfRule type="expression" dxfId="103" priority="30">
       <formula>AND(TRIM($A2)="Denied",$K2&lt;&gt;"")</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="101" priority="27">
+    <cfRule type="expression" dxfId="101" priority="28">
       <formula>TRIM($A2)="Rejected"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="102" priority="28">
+    <cfRule type="expression" dxfId="102" priority="29">
       <formula>TRIM($A2)="Not found"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -17474,19 +17595,19 @@
     <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" s="9" t="str">
         <f>"    3 - Due in 31+ days: "&amp;SUM(COUNTIFS(BH!$L$2:$L$1000,"&gt;30"),COUNTIFS(DME!$L$2:$L$1000,"&gt;30"),COUNTIFS(GAE!$L$2:$L$1000,"&gt;30"),COUNTIFS(ORTHO!$L$2:$L$1000,"&gt;30"),COUNTIFS(US!$L$2:$L$1000,"&gt;30"))</f>
-        <v>    3 - Due in 31+ days: 37</v>
+        <v>    3 - Due in 31+ days: 28</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" s="9" t="str">
         <f>"    4 - Past deadline: "&amp;SUM(COUNTIFS(BH!$L$2:$L$1000,"&lt;0"),COUNTIFS(DME!$L$2:$L$1000,"&lt;0"),COUNTIFS(GAE!$L$2:$L$1000,"&lt;0"),COUNTIFS(ORTHO!$L$2:$L$1000,"&lt;0"),COUNTIFS(US!$L$2:$L$1000,"&lt;0"))</f>
-        <v>    4 - Past deadline: 58</v>
+        <v>    4 - Past deadline: 40</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" s="9" t="str">
-        <f>"    5 - No limit on file: "&amp;SUM(COUNTIFS(BH!$D$2:$D$1000,"&lt;&gt;",BH!$L$2:$L$1000,""),COUNTIFS(DME!$D$2:$D$1000,"&lt;&gt;",DME!$L$2:$L$1000,""),COUNTIFS(GAE!$D$2:$D$1000,"&lt;&gt;",GAE!$L$2:$L$1000,""),COUNTIFS(ORTHO!$D$2:$D$1000,"&lt;&gt;",ORTHO!$L$2:$L$1000,""),COUNTIFS(US!$D$2:$D$1000,"&lt;&gt;",US!$L$2:$L$1000,""))</f>
-        <v>    5 - No limit on file: 11</v>
+        <f>"    5 - No limit on file: "&amp;SUM(SUMPRODUCT((BH!$D$2:$D$1000&lt;&gt;"")*(BH!$L$2:$L$1000="")*(1-(TRIM(BH!$A$2:$A$1000)="Finalized")*(BH!$K$2:$K$1000&lt;&gt;""))),SUMPRODUCT((DME!$D$2:$D$1000&lt;&gt;"")*(DME!$L$2:$L$1000="")*(1-(TRIM(DME!$A$2:$A$1000)="Finalized")*(DME!$K$2:$K$1000&lt;&gt;""))),SUMPRODUCT((GAE!$D$2:$D$1000&lt;&gt;"")*(GAE!$L$2:$L$1000="")*(1-(TRIM(GAE!$A$2:$A$1000)="Finalized")*(GAE!$K$2:$K$1000&lt;&gt;""))),SUMPRODUCT((ORTHO!$D$2:$D$1000&lt;&gt;"")*(ORTHO!$L$2:$L$1000="")*(1-(TRIM(ORTHO!$A$2:$A$1000)="Finalized")*(ORTHO!$K$2:$K$1000&lt;&gt;""))),SUMPRODUCT((US!$D$2:$D$1000&lt;&gt;"")*(US!$L$2:$L$1000="")*(1-(TRIM(US!$A$2:$A$1000)="Finalized")*(US!$K$2:$K$1000&lt;&gt;""))))</f>
+        <v>    5 - No limit on file: 10</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.25">
